--- a/KYZ/Plugins/TopSky/Documentation/Developer/TopSky_Developer_Guide_Settings.xlsx
+++ b/KYZ/Plugins/TopSky/Documentation/Developer/TopSky_Developer_Guide_Settings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Juha\Documents\Office Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5C2392A-0969-4F4A-A493-3F1C11180717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FF18BFC-28AB-4D17-801B-583359502B92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TopSky 2.6" sheetId="1" r:id="rId1"/>
@@ -6011,9 +6011,6 @@
     <t>Format of the NAT Track Messages</t>
   </si>
   <si>
-    <t>0 (original track message), 1 (json format from natTrak)</t>
-  </si>
-  <si>
     <t>System_Toggle_Units_In_Level_Menus</t>
   </si>
   <si>
@@ -7419,9 +7416,6 @@
   </si>
   <si>
     <t>NOTAM data source</t>
-  </si>
-  <si>
-    <t>https://notams.aim.faa.gov/nat.html</t>
   </si>
   <si>
     <t>Window_CARD_Slider_Time_Max</t>
@@ -8332,6 +8326,12 @@
   </si>
   <si>
     <t>FAST_Remove_After_LDG</t>
+  </si>
+  <si>
+    <t>https://nms.aim.faa.gov/datanat/nat.json</t>
+  </si>
+  <si>
+    <t>0 (json format from FAA), 1 (json format from natTrak)</t>
   </si>
 </sst>
 </file>
@@ -12112,7 +12112,7 @@
         <v>399</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2247</v>
+        <v>2246</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>137</v>
@@ -12133,7 +12133,7 @@
         <v>559</v>
       </c>
       <c r="B3" t="s">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="C3" t="s">
         <v>721</v>
@@ -12153,7 +12153,7 @@
         <v>1042</v>
       </c>
       <c r="B5" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="C5" t="s">
         <v>721</v>
@@ -12237,13 +12237,13 @@
         <v>1261</v>
       </c>
       <c r="B10" t="s">
-        <v>2710</v>
+        <v>2708</v>
       </c>
       <c r="C10" t="s">
         <v>721</v>
       </c>
       <c r="D10" t="s">
-        <v>2469</v>
+        <v>2467</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>721</v>
@@ -12348,7 +12348,7 @@
         <v>721</v>
       </c>
       <c r="D17" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>139</v>
@@ -12374,7 +12374,7 @@
         <v>721</v>
       </c>
       <c r="D18" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>139</v>
@@ -12457,7 +12457,7 @@
         <v>1031</v>
       </c>
       <c r="B22" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="C22" t="s">
         <v>721</v>
@@ -12509,7 +12509,7 @@
         <v>721</v>
       </c>
       <c r="D24" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>139</v>
@@ -12535,7 +12535,7 @@
         <v>721</v>
       </c>
       <c r="D25" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>139</v>
@@ -12552,10 +12552,10 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
       <c r="B26" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="C26" t="s">
         <v>721</v>
@@ -12606,16 +12606,16 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>2266</v>
+      </c>
+      <c r="B29" t="s">
+        <v>2270</v>
+      </c>
+      <c r="C29" t="s">
+        <v>721</v>
+      </c>
+      <c r="D29" t="s">
         <v>2267</v>
-      </c>
-      <c r="B29" t="s">
-        <v>2271</v>
-      </c>
-      <c r="C29" t="s">
-        <v>721</v>
-      </c>
-      <c r="D29" t="s">
-        <v>2268</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>721</v>
@@ -12625,16 +12625,16 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B30" t="s">
         <v>2269</v>
       </c>
-      <c r="B30" t="s">
-        <v>2270</v>
-      </c>
       <c r="C30" t="s">
         <v>721</v>
       </c>
       <c r="D30" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>721</v>
@@ -12653,7 +12653,7 @@
         <v>721</v>
       </c>
       <c r="D31" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>139</v>
@@ -12679,7 +12679,7 @@
         <v>721</v>
       </c>
       <c r="D32" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>139</v>
@@ -12699,13 +12699,13 @@
         <v>949</v>
       </c>
       <c r="B33" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C33" t="s">
         <v>721</v>
       </c>
       <c r="D33" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>139</v>
@@ -12890,7 +12890,7 @@
         <v>1581</v>
       </c>
       <c r="B44" t="s">
-        <v>2661</v>
+        <v>2659</v>
       </c>
       <c r="C44" t="s">
         <v>721</v>
@@ -12979,7 +12979,7 @@
         <v>1939</v>
       </c>
       <c r="B49" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="C49" t="s">
         <v>721</v>
@@ -13105,10 +13105,10 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B55" t="s">
         <v>2565</v>
-      </c>
-      <c r="B55" t="s">
-        <v>2567</v>
       </c>
       <c r="C55" t="s">
         <v>721</v>
@@ -13131,10 +13131,10 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B56" t="s">
         <v>2566</v>
-      </c>
-      <c r="B56" t="s">
-        <v>2568</v>
       </c>
       <c r="C56" t="s">
         <v>721</v>
@@ -13511,7 +13511,7 @@
         <v>238</v>
       </c>
       <c r="B73" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
       <c r="C73" t="s">
         <v>721</v>
@@ -13658,7 +13658,7 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B80" t="s">
         <v>1902</v>
@@ -13776,16 +13776,16 @@
         <v>721</v>
       </c>
       <c r="D85" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>721</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -13799,16 +13799,16 @@
         <v>721</v>
       </c>
       <c r="D86" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>721</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -13822,16 +13822,16 @@
         <v>721</v>
       </c>
       <c r="D87" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>721</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -13845,16 +13845,16 @@
         <v>721</v>
       </c>
       <c r="D88" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>721</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -13868,16 +13868,16 @@
         <v>721</v>
       </c>
       <c r="D89" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>721</v>
       </c>
       <c r="H89" s="2" t="s">
+        <v>2158</v>
+      </c>
+      <c r="I89" s="2" t="s">
         <v>2159</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>2160</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -13891,24 +13891,24 @@
         <v>721</v>
       </c>
       <c r="D90" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>721</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B91" t="s">
         <v>2169</v>
-      </c>
-      <c r="B91" t="s">
-        <v>2170</v>
       </c>
       <c r="C91" t="s">
         <v>721</v>
@@ -13948,7 +13948,7 @@
         <v>154</v>
       </c>
       <c r="B93" t="s">
-        <v>2447</v>
+        <v>2446</v>
       </c>
       <c r="C93" t="s">
         <v>721</v>
@@ -13971,10 +13971,10 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B94" t="s">
         <v>2445</v>
-      </c>
-      <c r="B94" t="s">
-        <v>2446</v>
       </c>
       <c r="C94" t="s">
         <v>721</v>
@@ -13997,10 +13997,10 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B95" t="s">
         <v>2380</v>
-      </c>
-      <c r="B95" t="s">
-        <v>2381</v>
       </c>
       <c r="C95" t="s">
         <v>721</v>
@@ -14017,10 +14017,10 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B96" t="s">
         <v>2441</v>
-      </c>
-      <c r="B96" t="s">
-        <v>2442</v>
       </c>
       <c r="C96" t="s">
         <v>721</v>
@@ -14031,16 +14031,16 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
       <c r="B98" t="s">
-        <v>2668</v>
+        <v>2666</v>
       </c>
       <c r="C98" t="s">
         <v>721</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>2579</v>
+        <v>2577</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>721</v>
@@ -14054,10 +14054,10 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
       <c r="B99" t="s">
-        <v>2670</v>
+        <v>2668</v>
       </c>
       <c r="C99" t="s">
         <v>721</v>
@@ -14069,7 +14069,7 @@
         <v>173</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>2671</v>
+        <v>2669</v>
       </c>
       <c r="H99" s="2">
         <v>50</v>
@@ -14080,10 +14080,10 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
       <c r="B100" t="s">
-        <v>2672</v>
+        <v>2670</v>
       </c>
       <c r="C100" t="s">
         <v>721</v>
@@ -14106,10 +14106,10 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
       <c r="B101" t="s">
-        <v>2704</v>
+        <v>2702</v>
       </c>
       <c r="C101" t="s">
         <v>721</v>
@@ -14132,7 +14132,7 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
       <c r="B103" t="s">
         <v>556</v>
@@ -14144,10 +14144,10 @@
         <v>129</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -14612,7 +14612,7 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="B127" t="s">
         <v>556</v>
@@ -14672,7 +14672,7 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="B130" t="s">
         <v>556</v>
@@ -14687,7 +14687,7 @@
         <v>58</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
@@ -14792,7 +14792,7 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
       <c r="B136" t="s">
         <v>556</v>
@@ -14807,12 +14807,12 @@
         <v>74</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
       <c r="B137" t="s">
         <v>556</v>
@@ -14827,12 +14827,12 @@
         <v>1622</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
       <c r="B138" t="s">
         <v>556</v>
@@ -14847,12 +14847,12 @@
         <v>1622</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
       <c r="B139" t="s">
         <v>556</v>
@@ -14864,15 +14864,15 @@
         <v>129</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="B140" t="s">
         <v>556</v>
@@ -14884,10 +14884,10 @@
         <v>129</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
@@ -14963,7 +14963,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="B145" t="s">
         <v>556</v>
@@ -15003,7 +15003,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
       <c r="B147" t="s">
         <v>556</v>
@@ -15015,12 +15015,12 @@
         <v>129</v>
       </c>
       <c r="I147" s="2" t="s">
-        <v>2061</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="B148" t="s">
         <v>556</v>
@@ -15032,7 +15032,7 @@
         <v>129</v>
       </c>
       <c r="I148" s="2" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
@@ -15192,7 +15192,7 @@
         <v>965</v>
       </c>
       <c r="I156" s="2" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -15232,7 +15232,7 @@
         <v>968</v>
       </c>
       <c r="I158" s="2" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
@@ -15542,7 +15542,7 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="B175" t="s">
         <v>556</v>
@@ -15557,12 +15557,12 @@
         <v>55</v>
       </c>
       <c r="I175" s="2" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="B176" t="s">
         <v>556</v>
@@ -15577,12 +15577,12 @@
         <v>68</v>
       </c>
       <c r="I176" s="2" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="B177" t="s">
         <v>556</v>
@@ -15597,12 +15597,12 @@
         <v>55</v>
       </c>
       <c r="I177" s="2" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="B178" t="s">
         <v>556</v>
@@ -15617,7 +15617,7 @@
         <v>55</v>
       </c>
       <c r="I178" s="2" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
@@ -15737,7 +15737,7 @@
         <v>637</v>
       </c>
       <c r="I184" s="2" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
@@ -16048,7 +16048,7 @@
         <v>129</v>
       </c>
       <c r="I200" s="2" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
@@ -16065,12 +16065,12 @@
         <v>129</v>
       </c>
       <c r="I201" s="2" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="B202" t="s">
         <v>556</v>
@@ -16082,10 +16082,10 @@
         <v>129</v>
       </c>
       <c r="H202" s="2" t="s">
+        <v>2143</v>
+      </c>
+      <c r="I202" s="2" t="s">
         <v>2144</v>
-      </c>
-      <c r="I202" s="2" t="s">
-        <v>2145</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
@@ -16130,7 +16130,7 @@
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="B205" t="s">
         <v>556</v>
@@ -16142,10 +16142,10 @@
         <v>129</v>
       </c>
       <c r="H205" s="2" t="s">
+        <v>2152</v>
+      </c>
+      <c r="I205" s="2" t="s">
         <v>2153</v>
-      </c>
-      <c r="I205" s="2" t="s">
-        <v>2154</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
@@ -16225,7 +16225,7 @@
         <v>1628</v>
       </c>
       <c r="I209" s="2" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
@@ -16684,7 +16684,7 @@
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="B233" t="s">
         <v>556</v>
@@ -17081,12 +17081,12 @@
         <v>129</v>
       </c>
       <c r="I253" s="2" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="B254" t="s">
         <v>556</v>
@@ -17098,15 +17098,15 @@
         <v>129</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="I254" s="2" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="B255" t="s">
         <v>556</v>
@@ -17118,15 +17118,15 @@
         <v>129</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="I255" s="2" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="B256" t="s">
         <v>556</v>
@@ -17138,15 +17138,15 @@
         <v>129</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
       <c r="I256" s="2" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
       <c r="B257" t="s">
         <v>556</v>
@@ -17158,10 +17158,10 @@
         <v>129</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="I257" s="2" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
@@ -17698,7 +17698,7 @@
         <v>73</v>
       </c>
       <c r="I284" s="2" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
@@ -17869,16 +17869,16 @@
     </row>
     <row r="294" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="B294" t="s">
-        <v>2474</v>
+        <v>2472</v>
       </c>
       <c r="C294" t="s">
         <v>721</v>
       </c>
       <c r="D294" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="E294" s="4" t="s">
         <v>721</v>
@@ -17892,16 +17892,16 @@
     </row>
     <row r="295" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B295" t="s">
+        <v>2469</v>
+      </c>
+      <c r="C295" t="s">
+        <v>721</v>
+      </c>
+      <c r="D295" t="s">
         <v>2470</v>
-      </c>
-      <c r="B295" t="s">
-        <v>2471</v>
-      </c>
-      <c r="C295" t="s">
-        <v>721</v>
-      </c>
-      <c r="D295" t="s">
-        <v>2472</v>
       </c>
       <c r="E295" s="4" t="s">
         <v>721</v>
@@ -17915,16 +17915,16 @@
     </row>
     <row r="296" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
       <c r="B296" t="s">
-        <v>2476</v>
+        <v>2474</v>
       </c>
       <c r="C296" t="s">
         <v>721</v>
       </c>
       <c r="D296" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="E296" s="4" t="s">
         <v>721</v>
@@ -17938,16 +17938,16 @@
     </row>
     <row r="297" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="B297" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
       <c r="C297" t="s">
         <v>721</v>
       </c>
       <c r="D297" t="s">
-        <v>2472</v>
+        <v>2470</v>
       </c>
       <c r="E297" s="4" t="s">
         <v>721</v>
@@ -17961,10 +17961,10 @@
     </row>
     <row r="298" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="B298" t="s">
-        <v>2482</v>
+        <v>2480</v>
       </c>
       <c r="C298" t="s">
         <v>721</v>
@@ -17984,10 +17984,10 @@
     </row>
     <row r="299" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
       <c r="B299" t="s">
-        <v>2481</v>
+        <v>2479</v>
       </c>
       <c r="C299" t="s">
         <v>721</v>
@@ -18053,10 +18053,10 @@
     </row>
     <row r="302" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B302" t="s">
         <v>2275</v>
-      </c>
-      <c r="B302" t="s">
-        <v>2276</v>
       </c>
       <c r="C302" t="s">
         <v>721</v>
@@ -18068,7 +18068,7 @@
         <v>140</v>
       </c>
       <c r="F302" s="4" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="H302" s="2">
         <v>60</v>
@@ -18159,10 +18159,10 @@
     </row>
     <row r="307" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B307" t="s">
         <v>2127</v>
-      </c>
-      <c r="B307" t="s">
-        <v>2128</v>
       </c>
       <c r="C307" t="s">
         <v>721</v>
@@ -18179,16 +18179,16 @@
     </row>
     <row r="308" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
       <c r="B308" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
       <c r="C308" t="s">
         <v>721</v>
       </c>
       <c r="D308" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
       <c r="E308" s="4" t="s">
         <v>721</v>
@@ -18202,16 +18202,16 @@
     </row>
     <row r="309" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B309" t="s">
         <v>2135</v>
       </c>
-      <c r="B309" t="s">
-        <v>2136</v>
-      </c>
       <c r="C309" t="s">
         <v>721</v>
       </c>
       <c r="D309" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="E309" s="4" t="s">
         <v>721</v>
@@ -18225,16 +18225,16 @@
     </row>
     <row r="310" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B310" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C310" t="s">
+        <v>721</v>
+      </c>
+      <c r="D310" t="s">
         <v>2166</v>
-      </c>
-      <c r="B310" t="s">
-        <v>2168</v>
-      </c>
-      <c r="C310" t="s">
-        <v>721</v>
-      </c>
-      <c r="D310" t="s">
-        <v>2167</v>
       </c>
       <c r="E310" s="4" t="s">
         <v>721</v>
@@ -18248,16 +18248,16 @@
     </row>
     <row r="311" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B311" t="s">
         <v>2132</v>
       </c>
-      <c r="B311" t="s">
+      <c r="C311" t="s">
+        <v>721</v>
+      </c>
+      <c r="D311" t="s">
         <v>2133</v>
-      </c>
-      <c r="C311" t="s">
-        <v>721</v>
-      </c>
-      <c r="D311" t="s">
-        <v>2134</v>
       </c>
       <c r="E311" s="4" t="s">
         <v>721</v>
@@ -18271,10 +18271,10 @@
     </row>
     <row r="312" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B312" t="s">
         <v>2385</v>
-      </c>
-      <c r="B312" t="s">
-        <v>2386</v>
       </c>
       <c r="C312" t="s">
         <v>721</v>
@@ -18294,7 +18294,7 @@
         <v>809</v>
       </c>
       <c r="B313" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="C313" t="s">
         <v>721</v>
@@ -18314,7 +18314,7 @@
         <v>810</v>
       </c>
       <c r="B314" t="s">
-        <v>2129</v>
+        <v>2128</v>
       </c>
       <c r="C314" t="s">
         <v>721</v>
@@ -18340,7 +18340,7 @@
         <v>811</v>
       </c>
       <c r="B315" t="s">
-        <v>2130</v>
+        <v>2129</v>
       </c>
       <c r="C315" t="s">
         <v>721</v>
@@ -18363,10 +18363,10 @@
     </row>
     <row r="316" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="B316" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="C316" t="s">
         <v>721</v>
@@ -18389,10 +18389,10 @@
     </row>
     <row r="317" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="B317" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="C317" t="s">
         <v>721</v>
@@ -18415,10 +18415,10 @@
     </row>
     <row r="318" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="B318" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="C318" t="s">
         <v>721</v>
@@ -18441,10 +18441,10 @@
     </row>
     <row r="319" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B319" t="s">
         <v>2367</v>
-      </c>
-      <c r="B319" t="s">
-        <v>2368</v>
       </c>
       <c r="C319" t="s">
         <v>721</v>
@@ -18461,10 +18461,10 @@
     </row>
     <row r="320" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B320" t="s">
         <v>2363</v>
-      </c>
-      <c r="B320" t="s">
-        <v>2364</v>
       </c>
       <c r="C320" t="s">
         <v>721</v>
@@ -18487,10 +18487,10 @@
     </row>
     <row r="321" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B321" t="s">
         <v>2365</v>
-      </c>
-      <c r="B321" t="s">
-        <v>2366</v>
       </c>
       <c r="C321" t="s">
         <v>721</v>
@@ -18565,10 +18565,10 @@
         <v>130</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="I324" s="2" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
     </row>
     <row r="325" spans="1:9" x14ac:dyDescent="0.25">
@@ -18585,10 +18585,10 @@
         <v>130</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="I325" s="2" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
     </row>
     <row r="326" spans="1:9" x14ac:dyDescent="0.25">
@@ -18613,10 +18613,10 @@
     </row>
     <row r="327" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
       <c r="B327" t="s">
-        <v>2733</v>
+        <v>2731</v>
       </c>
       <c r="C327" t="s">
         <v>721</v>
@@ -18625,10 +18625,10 @@
         <v>130</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="I327" s="2" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
     </row>
     <row r="328" spans="1:9" x14ac:dyDescent="0.25">
@@ -18645,10 +18645,10 @@
         <v>130</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="I328" s="2" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
     </row>
     <row r="329" spans="1:9" x14ac:dyDescent="0.25">
@@ -18665,10 +18665,10 @@
         <v>130</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>2742</v>
+        <v>2740</v>
       </c>
       <c r="I329" s="2" t="s">
-        <v>2742</v>
+        <v>2740</v>
       </c>
     </row>
     <row r="330" spans="1:9" x14ac:dyDescent="0.25">
@@ -18685,10 +18685,10 @@
         <v>130</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
       <c r="I330" s="2" t="s">
-        <v>2744</v>
+        <v>2742</v>
       </c>
     </row>
     <row r="331" spans="1:9" x14ac:dyDescent="0.25">
@@ -18705,10 +18705,10 @@
         <v>130</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="I331" s="2" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
     </row>
     <row r="332" spans="1:9" x14ac:dyDescent="0.25">
@@ -18725,15 +18725,15 @@
         <v>130</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="I332" s="2" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
     </row>
     <row r="333" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
       <c r="B333" t="s">
         <v>1325</v>
@@ -18745,10 +18745,10 @@
         <v>130</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="I333" s="2" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="334" spans="1:9" x14ac:dyDescent="0.25">
@@ -18765,10 +18765,10 @@
         <v>130</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
       <c r="I334" s="2" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
     </row>
     <row r="335" spans="1:9" x14ac:dyDescent="0.25">
@@ -18785,10 +18785,10 @@
         <v>130</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
       <c r="I335" s="2" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
     </row>
     <row r="336" spans="1:9" x14ac:dyDescent="0.25">
@@ -18951,7 +18951,7 @@
         <v>1431</v>
       </c>
       <c r="B344" t="s">
-        <v>2662</v>
+        <v>2660</v>
       </c>
       <c r="C344" t="s">
         <v>721</v>
@@ -18988,16 +18988,16 @@
     </row>
     <row r="346" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
+        <v>2271</v>
+      </c>
+      <c r="B346" t="s">
         <v>2272</v>
       </c>
-      <c r="B346" t="s">
+      <c r="C346" t="s">
+        <v>721</v>
+      </c>
+      <c r="D346" t="s">
         <v>2273</v>
-      </c>
-      <c r="C346" t="s">
-        <v>721</v>
-      </c>
-      <c r="D346" t="s">
-        <v>2274</v>
       </c>
       <c r="E346" s="4" t="s">
         <v>721</v>
@@ -19256,10 +19256,10 @@
     </row>
     <row r="358" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B358" t="s">
         <v>2348</v>
-      </c>
-      <c r="B358" t="s">
-        <v>2349</v>
       </c>
       <c r="C358" t="s">
         <v>721</v>
@@ -19285,7 +19285,7 @@
         <v>721</v>
       </c>
       <c r="D359" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="E359" s="4" t="s">
         <v>721</v>
@@ -19299,10 +19299,10 @@
     </row>
     <row r="360" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B360" t="s">
         <v>2214</v>
-      </c>
-      <c r="B360" t="s">
-        <v>2215</v>
       </c>
       <c r="C360" t="s">
         <v>721</v>
@@ -19319,10 +19319,10 @@
     </row>
     <row r="361" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
+        <v>2215</v>
+      </c>
+      <c r="B361" t="s">
         <v>2216</v>
-      </c>
-      <c r="B361" t="s">
-        <v>2217</v>
       </c>
       <c r="C361" t="s">
         <v>721</v>
@@ -19339,10 +19339,10 @@
     </row>
     <row r="362" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B362" t="s">
         <v>2218</v>
-      </c>
-      <c r="B362" t="s">
-        <v>2219</v>
       </c>
       <c r="C362" t="s">
         <v>721</v>
@@ -19359,10 +19359,10 @@
     </row>
     <row r="363" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
+        <v>2219</v>
+      </c>
+      <c r="B363" t="s">
         <v>2220</v>
-      </c>
-      <c r="B363" t="s">
-        <v>2221</v>
       </c>
       <c r="C363" t="s">
         <v>721</v>
@@ -19379,10 +19379,10 @@
     </row>
     <row r="364" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B364" t="s">
         <v>2222</v>
-      </c>
-      <c r="B364" t="s">
-        <v>2223</v>
       </c>
       <c r="C364" t="s">
         <v>721</v>
@@ -19399,10 +19399,10 @@
     </row>
     <row r="365" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="B365" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="C365" t="s">
         <v>721</v>
@@ -19419,10 +19419,10 @@
     </row>
     <row r="366" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B366" t="s">
         <v>2225</v>
-      </c>
-      <c r="B366" t="s">
-        <v>2226</v>
       </c>
       <c r="C366" t="s">
         <v>721</v>
@@ -19439,10 +19439,10 @@
     </row>
     <row r="367" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B367" t="s">
         <v>2227</v>
-      </c>
-      <c r="B367" t="s">
-        <v>2228</v>
       </c>
       <c r="C367" t="s">
         <v>721</v>
@@ -19462,7 +19462,7 @@
         <v>94</v>
       </c>
       <c r="B368" t="s">
-        <v>2078</v>
+        <v>2077</v>
       </c>
       <c r="C368" t="s">
         <v>721</v>
@@ -19482,7 +19482,7 @@
         <v>93</v>
       </c>
       <c r="B369" t="s">
-        <v>2079</v>
+        <v>2078</v>
       </c>
       <c r="C369" t="s">
         <v>721</v>
@@ -19502,7 +19502,7 @@
         <v>95</v>
       </c>
       <c r="B370" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="C370" t="s">
         <v>721</v>
@@ -19522,7 +19522,7 @@
         <v>96</v>
       </c>
       <c r="B371" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="C371" t="s">
         <v>721</v>
@@ -19542,7 +19542,7 @@
         <v>102</v>
       </c>
       <c r="B372" t="s">
-        <v>2082</v>
+        <v>2081</v>
       </c>
       <c r="C372" t="s">
         <v>721</v>
@@ -19562,7 +19562,7 @@
         <v>98</v>
       </c>
       <c r="B373" t="s">
-        <v>2083</v>
+        <v>2082</v>
       </c>
       <c r="C373" t="s">
         <v>721</v>
@@ -19582,7 +19582,7 @@
         <v>100</v>
       </c>
       <c r="B374" t="s">
-        <v>2084</v>
+        <v>2083</v>
       </c>
       <c r="C374" t="s">
         <v>721</v>
@@ -19602,7 +19602,7 @@
         <v>101</v>
       </c>
       <c r="B375" t="s">
-        <v>2085</v>
+        <v>2084</v>
       </c>
       <c r="C375" t="s">
         <v>721</v>
@@ -19622,7 +19622,7 @@
         <v>97</v>
       </c>
       <c r="B376" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="C376" t="s">
         <v>721</v>
@@ -19642,7 +19642,7 @@
         <v>99</v>
       </c>
       <c r="B377" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="C377" t="s">
         <v>721</v>
@@ -19659,10 +19659,10 @@
     </row>
     <row r="379" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="B379" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="C379" t="s">
         <v>721</v>
@@ -19679,16 +19679,16 @@
     </row>
     <row r="380" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B380" t="s">
+        <v>2508</v>
+      </c>
+      <c r="C380" t="s">
+        <v>721</v>
+      </c>
+      <c r="D380" t="s">
         <v>2509</v>
-      </c>
-      <c r="B380" t="s">
-        <v>2510</v>
-      </c>
-      <c r="C380" t="s">
-        <v>721</v>
-      </c>
-      <c r="D380" t="s">
-        <v>2511</v>
       </c>
       <c r="E380" s="4" t="s">
         <v>721</v>
@@ -19702,16 +19702,16 @@
     </row>
     <row r="381" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B381" t="s">
+        <v>2511</v>
+      </c>
+      <c r="C381" t="s">
+        <v>721</v>
+      </c>
+      <c r="D381" t="s">
         <v>2512</v>
-      </c>
-      <c r="B381" t="s">
-        <v>2513</v>
-      </c>
-      <c r="C381" t="s">
-        <v>721</v>
-      </c>
-      <c r="D381" t="s">
-        <v>2514</v>
       </c>
       <c r="E381" s="4" t="s">
         <v>721</v>
@@ -19725,16 +19725,16 @@
     </row>
     <row r="382" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B382" t="s">
+        <v>2514</v>
+      </c>
+      <c r="C382" t="s">
+        <v>721</v>
+      </c>
+      <c r="D382" t="s">
         <v>2515</v>
-      </c>
-      <c r="B382" t="s">
-        <v>2516</v>
-      </c>
-      <c r="C382" t="s">
-        <v>721</v>
-      </c>
-      <c r="D382" t="s">
-        <v>2517</v>
       </c>
       <c r="E382" s="4" t="s">
         <v>721</v>
@@ -19748,10 +19748,10 @@
     </row>
     <row r="383" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
       <c r="B383" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="C383" t="s">
         <v>721</v>
@@ -19768,10 +19768,10 @@
     </row>
     <row r="384" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="B384" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="C384" t="s">
         <v>721</v>
@@ -19788,10 +19788,10 @@
     </row>
     <row r="385" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
       <c r="B385" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="C385" t="s">
         <v>721</v>
@@ -19814,10 +19814,10 @@
     </row>
     <row r="386" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="B386" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="C386" t="s">
         <v>721</v>
@@ -19840,10 +19840,10 @@
     </row>
     <row r="387" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="B387" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="C387" t="s">
         <v>721</v>
@@ -19866,10 +19866,10 @@
     </row>
     <row r="388" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="B388" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="C388" t="s">
         <v>721</v>
@@ -20110,7 +20110,7 @@
         <v>390</v>
       </c>
       <c r="B400" t="s">
-        <v>2142</v>
+        <v>2141</v>
       </c>
       <c r="C400" t="s">
         <v>721</v>
@@ -20262,10 +20262,10 @@
     </row>
     <row r="408" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="B408" t="s">
-        <v>2122</v>
+        <v>2121</v>
       </c>
       <c r="C408" t="s">
         <v>721</v>
@@ -20288,10 +20288,10 @@
     </row>
     <row r="409" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="B409" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="C409" t="s">
         <v>721</v>
@@ -20314,10 +20314,10 @@
     </row>
     <row r="410" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B410" t="s">
-        <v>2124</v>
+        <v>2123</v>
       </c>
       <c r="C410" t="s">
         <v>721</v>
@@ -20340,10 +20340,10 @@
     </row>
     <row r="411" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="B411" t="s">
-        <v>2125</v>
+        <v>2124</v>
       </c>
       <c r="C411" t="s">
         <v>721</v>
@@ -20366,10 +20366,10 @@
     </row>
     <row r="412" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
       <c r="B412" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="C412" t="s">
         <v>721</v>
@@ -20392,10 +20392,10 @@
     </row>
     <row r="413" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B413" t="s">
         <v>2117</v>
-      </c>
-      <c r="B413" t="s">
-        <v>2118</v>
       </c>
       <c r="C413" t="s">
         <v>721</v>
@@ -20447,7 +20447,7 @@
         <v>1332</v>
       </c>
       <c r="B415" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="C415" t="s">
         <v>721</v>
@@ -20499,7 +20499,7 @@
         <v>948</v>
       </c>
       <c r="B417" t="s">
-        <v>2088</v>
+        <v>2087</v>
       </c>
       <c r="C417" t="s">
         <v>721</v>
@@ -20522,16 +20522,16 @@
     </row>
     <row r="419" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
       <c r="B419" t="s">
+        <v>2485</v>
+      </c>
+      <c r="C419" t="s">
+        <v>721</v>
+      </c>
+      <c r="D419" t="s">
         <v>2487</v>
-      </c>
-      <c r="C419" t="s">
-        <v>721</v>
-      </c>
-      <c r="D419" t="s">
-        <v>2489</v>
       </c>
       <c r="E419" s="4" t="s">
         <v>721</v>
@@ -20539,10 +20539,10 @@
     </row>
     <row r="421" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B421" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="C421" t="s">
         <v>721</v>
@@ -20553,10 +20553,10 @@
     </row>
     <row r="422" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B422" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="C422" t="s">
         <v>721</v>
@@ -20567,10 +20567,10 @@
     </row>
     <row r="423" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="B423" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="C423" t="s">
         <v>721</v>
@@ -20587,10 +20587,10 @@
     </row>
     <row r="424" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B424" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="C424" t="s">
         <v>721</v>
@@ -20601,10 +20601,10 @@
     </row>
     <row r="425" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="B425" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="C425" t="s">
         <v>721</v>
@@ -20618,7 +20618,7 @@
         <v>1933</v>
       </c>
       <c r="B426" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="C426" t="s">
         <v>721</v>
@@ -20643,10 +20643,10 @@
     </row>
     <row r="430" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B430" t="s">
         <v>2104</v>
-      </c>
-      <c r="B430" t="s">
-        <v>2105</v>
       </c>
       <c r="C430" t="s">
         <v>721</v>
@@ -20655,18 +20655,18 @@
         <v>130</v>
       </c>
       <c r="H430" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="I430" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
     </row>
     <row r="431" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B431" t="s">
         <v>2106</v>
-      </c>
-      <c r="B431" t="s">
-        <v>2107</v>
       </c>
       <c r="C431" t="s">
         <v>721</v>
@@ -20675,18 +20675,18 @@
         <v>130</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="I431" s="2" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
     </row>
     <row r="432" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="B432" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="C432" t="s">
         <v>721</v>
@@ -20703,10 +20703,10 @@
     </row>
     <row r="433" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B433" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="C433" t="s">
         <v>721</v>
@@ -20723,10 +20723,10 @@
     </row>
     <row r="434" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
       <c r="B434" t="s">
-        <v>2179</v>
+        <v>2178</v>
       </c>
       <c r="C434" t="s">
         <v>721</v>
@@ -20743,10 +20743,10 @@
     </row>
     <row r="435" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
       <c r="B435" t="s">
-        <v>2180</v>
+        <v>2179</v>
       </c>
       <c r="C435" t="s">
         <v>721</v>
@@ -20795,10 +20795,10 @@
         <v>130</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
       <c r="I438" s="2" t="s">
-        <v>2451</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="439" spans="1:9" x14ac:dyDescent="0.25">
@@ -20815,10 +20815,10 @@
         <v>130</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="I439" s="2" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="440" spans="1:9" x14ac:dyDescent="0.25">
@@ -20875,10 +20875,10 @@
         <v>130</v>
       </c>
       <c r="H443" t="s">
-        <v>2457</v>
+        <v>2758</v>
       </c>
       <c r="I443" t="s">
-        <v>2457</v>
+        <v>2758</v>
       </c>
     </row>
     <row r="444" spans="1:9" x14ac:dyDescent="0.25">
@@ -20892,7 +20892,7 @@
         <v>721</v>
       </c>
       <c r="D444" t="s">
-        <v>1987</v>
+        <v>2759</v>
       </c>
       <c r="E444" s="4" t="s">
         <v>721</v>
@@ -20926,10 +20926,10 @@
     </row>
     <row r="447" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
       <c r="B447" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="C447" t="s">
         <v>721</v>
@@ -20938,7 +20938,7 @@
         <v>1428</v>
       </c>
       <c r="E447" s="4" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="F447" s="4" t="s">
         <v>1429</v>
@@ -20952,10 +20952,10 @@
     </row>
     <row r="448" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="B448" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="C448" t="s">
         <v>721</v>
@@ -20964,7 +20964,7 @@
         <v>1428</v>
       </c>
       <c r="E448" s="4" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="F448" s="4" t="s">
         <v>1429</v>
@@ -20978,10 +20978,10 @@
     </row>
     <row r="449" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="B449" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="C449" t="s">
         <v>721</v>
@@ -20990,7 +20990,7 @@
         <v>1428</v>
       </c>
       <c r="E449" s="4" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="F449" s="4" t="s">
         <v>1429</v>
@@ -21004,10 +21004,10 @@
     </row>
     <row r="450" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="B450" t="s">
-        <v>2193</v>
+        <v>2192</v>
       </c>
       <c r="C450" t="s">
         <v>721</v>
@@ -21016,7 +21016,7 @@
         <v>1428</v>
       </c>
       <c r="E450" s="4" t="s">
-        <v>2192</v>
+        <v>2191</v>
       </c>
       <c r="F450" s="4" t="s">
         <v>1429</v>
@@ -21030,10 +21030,10 @@
     </row>
     <row r="451" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B451" t="s">
         <v>2190</v>
-      </c>
-      <c r="B451" t="s">
-        <v>2191</v>
       </c>
       <c r="C451" t="s">
         <v>721</v>
@@ -21090,16 +21090,16 @@
     </row>
     <row r="455" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B455" t="s">
         <v>2455</v>
       </c>
-      <c r="B455" t="s">
-        <v>2456</v>
-      </c>
       <c r="C455" t="s">
         <v>721</v>
       </c>
       <c r="D455" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="E455" s="4" t="s">
         <v>721</v>
@@ -21217,10 +21217,10 @@
     </row>
     <row r="463" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B463" t="s">
         <v>2174</v>
-      </c>
-      <c r="B463" t="s">
-        <v>2175</v>
       </c>
       <c r="C463" t="s">
         <v>721</v>
@@ -21229,24 +21229,24 @@
         <v>130</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
       <c r="I463" s="2" t="s">
-        <v>2449</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="465" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
       <c r="B465" t="s">
-        <v>2488</v>
+        <v>2486</v>
       </c>
       <c r="C465" t="s">
         <v>721</v>
       </c>
       <c r="D465" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="E465" s="4" t="s">
         <v>721</v>
@@ -21286,10 +21286,10 @@
         <v>130</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
       <c r="I468" s="2" t="s">
-        <v>2450</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="469" spans="1:9" x14ac:dyDescent="0.25">
@@ -21306,10 +21306,10 @@
         <v>130</v>
       </c>
       <c r="H469" s="2" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
       <c r="I469" s="2" t="s">
-        <v>2448</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="470" spans="1:9" x14ac:dyDescent="0.25">
@@ -21354,16 +21354,16 @@
     </row>
     <row r="473" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B473" t="s">
         <v>2070</v>
       </c>
-      <c r="B473" t="s">
-        <v>2071</v>
-      </c>
       <c r="C473" t="s">
         <v>721</v>
       </c>
       <c r="D473" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="E473" s="4" t="s">
         <v>721</v>
@@ -21475,7 +21475,7 @@
         <v>1334</v>
       </c>
       <c r="B478" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="C478" t="s">
         <v>721</v>
@@ -21492,16 +21492,16 @@
     </row>
     <row r="479" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B479" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C479" t="s">
+        <v>721</v>
+      </c>
+      <c r="D479" t="s">
         <v>2182</v>
-      </c>
-      <c r="B479" t="s">
-        <v>2184</v>
-      </c>
-      <c r="C479" t="s">
-        <v>721</v>
-      </c>
-      <c r="D479" t="s">
-        <v>2183</v>
       </c>
       <c r="E479" s="4" t="s">
         <v>721</v>
@@ -21610,13 +21610,13 @@
         <v>120</v>
       </c>
       <c r="B484" t="s">
-        <v>2164</v>
+        <v>2163</v>
       </c>
       <c r="C484" t="s">
         <v>721</v>
       </c>
       <c r="D484" t="s">
-        <v>2163</v>
+        <v>2162</v>
       </c>
       <c r="E484" s="4" t="s">
         <v>721</v>
@@ -21926,10 +21926,10 @@
     </row>
     <row r="498" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B498" t="s">
         <v>1990</v>
-      </c>
-      <c r="B498" t="s">
-        <v>1991</v>
       </c>
       <c r="C498" t="s">
         <v>721</v>
@@ -22021,10 +22021,10 @@
     </row>
     <row r="502" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B502" t="s">
         <v>2137</v>
-      </c>
-      <c r="B502" t="s">
-        <v>2138</v>
       </c>
       <c r="C502" t="s">
         <v>721</v>
@@ -22033,7 +22033,7 @@
         <v>130</v>
       </c>
       <c r="I502" s="2" t="s">
-        <v>2750</v>
+        <v>2748</v>
       </c>
     </row>
     <row r="503" spans="1:9" x14ac:dyDescent="0.25">
@@ -22228,10 +22228,10 @@
     </row>
     <row r="511" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
       <c r="B511" t="s">
-        <v>2374</v>
+        <v>2373</v>
       </c>
       <c r="C511" t="s">
         <v>721</v>
@@ -22248,10 +22248,10 @@
     </row>
     <row r="512" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
       <c r="B512" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="C512" t="s">
         <v>721</v>
@@ -22344,7 +22344,7 @@
     </row>
     <row r="519" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B519" t="s">
         <v>569</v>
@@ -22361,7 +22361,7 @@
     </row>
     <row r="520" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B520" t="s">
         <v>569</v>
@@ -22378,7 +22378,7 @@
     </row>
     <row r="521" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B521" t="s">
         <v>569</v>
@@ -22395,7 +22395,7 @@
     </row>
     <row r="522" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B522" t="s">
         <v>569</v>
@@ -22412,7 +22412,7 @@
     </row>
     <row r="523" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B523" t="s">
         <v>569</v>
@@ -22429,7 +22429,7 @@
     </row>
     <row r="524" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B524" t="s">
         <v>569</v>
@@ -22446,7 +22446,7 @@
     </row>
     <row r="525" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B525" t="s">
         <v>569</v>
@@ -22463,7 +22463,7 @@
     </row>
     <row r="526" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
       <c r="B526" t="s">
         <v>569</v>
@@ -22480,7 +22480,7 @@
     </row>
     <row r="527" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
       <c r="B527" t="s">
         <v>569</v>
@@ -22497,7 +22497,7 @@
     </row>
     <row r="528" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
       <c r="B528" t="s">
         <v>569</v>
@@ -22514,7 +22514,7 @@
     </row>
     <row r="529" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B529" t="s">
         <v>569</v>
@@ -22531,7 +22531,7 @@
     </row>
     <row r="530" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B530" t="s">
         <v>569</v>
@@ -22548,7 +22548,7 @@
     </row>
     <row r="531" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B531" t="s">
         <v>569</v>
@@ -22565,7 +22565,7 @@
     </row>
     <row r="532" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B532" t="s">
         <v>569</v>
@@ -22582,7 +22582,7 @@
     </row>
     <row r="534" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B534" t="s">
         <v>1043</v>
@@ -22602,22 +22602,22 @@
     </row>
     <row r="536" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="B536" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C536" t="s">
+        <v>721</v>
+      </c>
+      <c r="D536" t="s">
         <v>2044</v>
-      </c>
-      <c r="C536" t="s">
-        <v>721</v>
-      </c>
-      <c r="D536" t="s">
-        <v>2045</v>
       </c>
       <c r="E536" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F536" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I536" s="11" t="s">
         <v>139</v>
@@ -22625,22 +22625,22 @@
     </row>
     <row r="537" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="B537" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C537" t="s">
+        <v>721</v>
+      </c>
+      <c r="D537" t="s">
         <v>2044</v>
-      </c>
-      <c r="C537" t="s">
-        <v>721</v>
-      </c>
-      <c r="D537" t="s">
-        <v>2045</v>
       </c>
       <c r="E537" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F537" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I537" s="11" t="s">
         <v>139</v>
@@ -22648,68 +22648,68 @@
     </row>
     <row r="538" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B538" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C538" t="s">
+        <v>721</v>
+      </c>
+      <c r="D538" t="s">
         <v>2044</v>
-      </c>
-      <c r="C538" t="s">
-        <v>721</v>
-      </c>
-      <c r="D538" t="s">
-        <v>2045</v>
       </c>
       <c r="E538" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F538" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I538" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="539" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B539" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C539" t="s">
+        <v>721</v>
+      </c>
+      <c r="D539" t="s">
         <v>2044</v>
-      </c>
-      <c r="C539" t="s">
-        <v>721</v>
-      </c>
-      <c r="D539" t="s">
-        <v>2045</v>
       </c>
       <c r="E539" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F539" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I539" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="540" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B540" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C540" t="s">
+        <v>721</v>
+      </c>
+      <c r="D540" t="s">
         <v>2044</v>
-      </c>
-      <c r="C540" t="s">
-        <v>721</v>
-      </c>
-      <c r="D540" t="s">
-        <v>2045</v>
       </c>
       <c r="E540" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F540" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I540" s="11" t="s">
         <v>139</v>
@@ -22717,16 +22717,16 @@
     </row>
     <row r="541" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B541" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C541" t="s">
+        <v>721</v>
+      </c>
+      <c r="D541" t="s">
         <v>2044</v>
-      </c>
-      <c r="C541" t="s">
-        <v>721</v>
-      </c>
-      <c r="D541" t="s">
-        <v>2045</v>
       </c>
       <c r="E541" s="4" t="s">
         <v>139</v>
@@ -22740,22 +22740,22 @@
     </row>
     <row r="542" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="B542" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C542" t="s">
+        <v>721</v>
+      </c>
+      <c r="D542" t="s">
         <v>2044</v>
-      </c>
-      <c r="C542" t="s">
-        <v>721</v>
-      </c>
-      <c r="D542" t="s">
-        <v>2045</v>
       </c>
       <c r="E542" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F542" s="4" t="s">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="I542" s="11" t="s">
         <v>139</v>
@@ -22763,108 +22763,108 @@
     </row>
     <row r="543" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="B543" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C543" t="s">
+        <v>721</v>
+      </c>
+      <c r="D543" t="s">
         <v>2044</v>
-      </c>
-      <c r="C543" t="s">
-        <v>721</v>
-      </c>
-      <c r="D543" t="s">
-        <v>2045</v>
       </c>
       <c r="E543" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F543" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I543" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="544" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B544" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C544" t="s">
+        <v>721</v>
+      </c>
+      <c r="D544" t="s">
         <v>2044</v>
-      </c>
-      <c r="C544" t="s">
-        <v>721</v>
-      </c>
-      <c r="D544" t="s">
-        <v>2045</v>
       </c>
       <c r="E544" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F544" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="I544" s="11" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="545" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B545" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C545" t="s">
+        <v>721</v>
+      </c>
+      <c r="D545" t="s">
         <v>2044</v>
-      </c>
-      <c r="C545" t="s">
-        <v>721</v>
-      </c>
-      <c r="D545" t="s">
-        <v>2045</v>
       </c>
       <c r="E545" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F545" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="I545" s="11" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="546" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B546" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C546" t="s">
+        <v>721</v>
+      </c>
+      <c r="D546" t="s">
         <v>2044</v>
-      </c>
-      <c r="C546" t="s">
-        <v>721</v>
-      </c>
-      <c r="D546" t="s">
-        <v>2045</v>
       </c>
       <c r="E546" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F546" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="I546" s="11" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="547" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B547" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C547" t="s">
+        <v>721</v>
+      </c>
+      <c r="D547" t="s">
         <v>2044</v>
-      </c>
-      <c r="C547" t="s">
-        <v>721</v>
-      </c>
-      <c r="D547" t="s">
-        <v>2045</v>
       </c>
       <c r="E547" s="4" t="s">
         <v>139</v>
@@ -22878,22 +22878,22 @@
     </row>
     <row r="548" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="B548" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C548" t="s">
+        <v>721</v>
+      </c>
+      <c r="D548" t="s">
         <v>2044</v>
-      </c>
-      <c r="C548" t="s">
-        <v>721</v>
-      </c>
-      <c r="D548" t="s">
-        <v>2045</v>
       </c>
       <c r="E548" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F548" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I548" s="11" t="s">
         <v>139</v>
@@ -22901,22 +22901,22 @@
     </row>
     <row r="549" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B549" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C549" t="s">
+        <v>721</v>
+      </c>
+      <c r="D549" t="s">
         <v>2044</v>
-      </c>
-      <c r="C549" t="s">
-        <v>721</v>
-      </c>
-      <c r="D549" t="s">
-        <v>2045</v>
       </c>
       <c r="E549" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F549" s="4" t="s">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="I549" s="11" t="s">
         <v>139</v>
@@ -22924,22 +22924,22 @@
     </row>
     <row r="550" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B550" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C550" t="s">
+        <v>721</v>
+      </c>
+      <c r="D550" t="s">
         <v>2044</v>
-      </c>
-      <c r="C550" t="s">
-        <v>721</v>
-      </c>
-      <c r="D550" t="s">
-        <v>2045</v>
       </c>
       <c r="E550" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F550" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I550" s="11" t="s">
         <v>139</v>
@@ -22947,22 +22947,22 @@
     </row>
     <row r="551" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B551" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C551" t="s">
+        <v>721</v>
+      </c>
+      <c r="D551" t="s">
         <v>2044</v>
-      </c>
-      <c r="C551" t="s">
-        <v>721</v>
-      </c>
-      <c r="D551" t="s">
-        <v>2045</v>
       </c>
       <c r="E551" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F551" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I551" s="11" t="s">
         <v>139</v>
@@ -22970,68 +22970,68 @@
     </row>
     <row r="552" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B552" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C552" t="s">
+        <v>721</v>
+      </c>
+      <c r="D552" t="s">
         <v>2044</v>
-      </c>
-      <c r="C552" t="s">
-        <v>721</v>
-      </c>
-      <c r="D552" t="s">
-        <v>2045</v>
       </c>
       <c r="E552" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F552" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I552" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="553" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B553" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C553" t="s">
+        <v>721</v>
+      </c>
+      <c r="D553" t="s">
         <v>2044</v>
-      </c>
-      <c r="C553" t="s">
-        <v>721</v>
-      </c>
-      <c r="D553" t="s">
-        <v>2045</v>
       </c>
       <c r="E553" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F553" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I553" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="554" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B554" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C554" t="s">
+        <v>721</v>
+      </c>
+      <c r="D554" t="s">
         <v>2044</v>
-      </c>
-      <c r="C554" t="s">
-        <v>721</v>
-      </c>
-      <c r="D554" t="s">
-        <v>2045</v>
       </c>
       <c r="E554" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F554" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I554" s="11" t="s">
         <v>139</v>
@@ -23042,22 +23042,22 @@
     </row>
     <row r="556" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B556" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C556" t="s">
+        <v>721</v>
+      </c>
+      <c r="D556" t="s">
         <v>2044</v>
-      </c>
-      <c r="C556" t="s">
-        <v>721</v>
-      </c>
-      <c r="D556" t="s">
-        <v>2045</v>
       </c>
       <c r="E556" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F556" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I556" s="11" t="s">
         <v>139</v>
@@ -23065,22 +23065,22 @@
     </row>
     <row r="557" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B557" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C557" t="s">
+        <v>721</v>
+      </c>
+      <c r="D557" t="s">
         <v>2044</v>
-      </c>
-      <c r="C557" t="s">
-        <v>721</v>
-      </c>
-      <c r="D557" t="s">
-        <v>2045</v>
       </c>
       <c r="E557" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F557" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I557" s="11" t="s">
         <v>139</v>
@@ -23088,22 +23088,22 @@
     </row>
     <row r="558" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B558" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C558" t="s">
+        <v>721</v>
+      </c>
+      <c r="D558" t="s">
         <v>2044</v>
-      </c>
-      <c r="C558" t="s">
-        <v>721</v>
-      </c>
-      <c r="D558" t="s">
-        <v>2045</v>
       </c>
       <c r="E558" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F558" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I558" s="11" t="s">
         <v>139</v>
@@ -23111,22 +23111,22 @@
     </row>
     <row r="559" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B559" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C559" t="s">
+        <v>721</v>
+      </c>
+      <c r="D559" t="s">
         <v>2044</v>
-      </c>
-      <c r="C559" t="s">
-        <v>721</v>
-      </c>
-      <c r="D559" t="s">
-        <v>2045</v>
       </c>
       <c r="E559" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F559" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I559" s="11" t="s">
         <v>139</v>
@@ -23134,22 +23134,22 @@
     </row>
     <row r="560" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B560" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C560" t="s">
+        <v>721</v>
+      </c>
+      <c r="D560" t="s">
         <v>2044</v>
-      </c>
-      <c r="C560" t="s">
-        <v>721</v>
-      </c>
-      <c r="D560" t="s">
-        <v>2045</v>
       </c>
       <c r="E560" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F560" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I560" s="11" t="s">
         <v>139</v>
@@ -23157,22 +23157,22 @@
     </row>
     <row r="561" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="B561" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C561" t="s">
+        <v>721</v>
+      </c>
+      <c r="D561" t="s">
         <v>2044</v>
-      </c>
-      <c r="C561" t="s">
-        <v>721</v>
-      </c>
-      <c r="D561" t="s">
-        <v>2045</v>
       </c>
       <c r="E561" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F561" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I561" s="11" t="s">
         <v>139</v>
@@ -23183,140 +23183,140 @@
     </row>
     <row r="563" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B563" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C563" t="s">
+        <v>721</v>
+      </c>
+      <c r="D563" t="s">
         <v>2044</v>
-      </c>
-      <c r="C563" t="s">
-        <v>721</v>
-      </c>
-      <c r="D563" t="s">
-        <v>2045</v>
       </c>
       <c r="E563" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F563" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I563" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="564" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B564" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C564" t="s">
+        <v>721</v>
+      </c>
+      <c r="D564" t="s">
         <v>2044</v>
-      </c>
-      <c r="C564" t="s">
-        <v>721</v>
-      </c>
-      <c r="D564" t="s">
-        <v>2045</v>
       </c>
       <c r="E564" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F564" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I564" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="565" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B565" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C565" t="s">
+        <v>721</v>
+      </c>
+      <c r="D565" t="s">
         <v>2044</v>
-      </c>
-      <c r="C565" t="s">
-        <v>721</v>
-      </c>
-      <c r="D565" t="s">
-        <v>2045</v>
       </c>
       <c r="E565" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F565" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I565" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="566" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B566" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C566" t="s">
+        <v>721</v>
+      </c>
+      <c r="D566" t="s">
         <v>2044</v>
-      </c>
-      <c r="C566" t="s">
-        <v>721</v>
-      </c>
-      <c r="D566" t="s">
-        <v>2045</v>
       </c>
       <c r="E566" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F566" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I566" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="567" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B567" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C567" t="s">
+        <v>721</v>
+      </c>
+      <c r="D567" t="s">
         <v>2044</v>
-      </c>
-      <c r="C567" t="s">
-        <v>721</v>
-      </c>
-      <c r="D567" t="s">
-        <v>2045</v>
       </c>
       <c r="E567" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F567" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I567" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="568" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="B568" t="s">
+        <v>2043</v>
+      </c>
+      <c r="C568" t="s">
+        <v>721</v>
+      </c>
+      <c r="D568" t="s">
         <v>2044</v>
-      </c>
-      <c r="C568" t="s">
-        <v>721</v>
-      </c>
-      <c r="D568" t="s">
-        <v>2045</v>
       </c>
       <c r="E568" s="4" t="s">
         <v>139</v>
       </c>
       <c r="F568" s="4" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="I568" s="11" t="s">
-        <v>2043</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="570" spans="1:9" x14ac:dyDescent="0.25">
@@ -23361,16 +23361,16 @@
     </row>
     <row r="573" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B573" t="s">
         <v>2396</v>
       </c>
-      <c r="B573" t="s">
+      <c r="C573" t="s">
+        <v>721</v>
+      </c>
+      <c r="D573" s="6" t="s">
         <v>2397</v>
-      </c>
-      <c r="C573" t="s">
-        <v>721</v>
-      </c>
-      <c r="D573" s="6" t="s">
-        <v>2398</v>
       </c>
       <c r="E573" s="4" t="s">
         <v>721</v>
@@ -23384,16 +23384,16 @@
     </row>
     <row r="574" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B574" t="s">
         <v>2390</v>
       </c>
-      <c r="B574" t="s">
+      <c r="C574" t="s">
+        <v>721</v>
+      </c>
+      <c r="D574" s="6" t="s">
         <v>2391</v>
-      </c>
-      <c r="C574" t="s">
-        <v>721</v>
-      </c>
-      <c r="D574" s="6" t="s">
-        <v>2392</v>
       </c>
       <c r="E574" s="4" t="s">
         <v>721</v>
@@ -23407,16 +23407,16 @@
     </row>
     <row r="575" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B575" t="s">
         <v>2393</v>
       </c>
-      <c r="B575" t="s">
+      <c r="C575" t="s">
+        <v>721</v>
+      </c>
+      <c r="D575" s="6" t="s">
         <v>2394</v>
-      </c>
-      <c r="C575" t="s">
-        <v>721</v>
-      </c>
-      <c r="D575" s="6" t="s">
-        <v>2395</v>
       </c>
       <c r="E575" s="4" t="s">
         <v>721</v>
@@ -23430,16 +23430,16 @@
     </row>
     <row r="577" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B577" t="s">
         <v>2399</v>
       </c>
-      <c r="B577" t="s">
-        <v>2400</v>
-      </c>
       <c r="C577" t="s">
         <v>721</v>
       </c>
       <c r="D577" s="6" t="s">
-        <v>2404</v>
+        <v>2403</v>
       </c>
       <c r="E577" s="4" t="s">
         <v>721</v>
@@ -23453,16 +23453,16 @@
     </row>
     <row r="578" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B578" t="s">
         <v>2401</v>
       </c>
-      <c r="B578" t="s">
+      <c r="C578" t="s">
+        <v>721</v>
+      </c>
+      <c r="D578" s="6" t="s">
         <v>2402</v>
-      </c>
-      <c r="C578" t="s">
-        <v>721</v>
-      </c>
-      <c r="D578" s="6" t="s">
-        <v>2403</v>
       </c>
       <c r="E578" s="4" t="s">
         <v>721</v>
@@ -23479,7 +23479,7 @@
         <v>1585</v>
       </c>
       <c r="B579" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="C579" t="s">
         <v>721</v>
@@ -23499,7 +23499,7 @@
         <v>1587</v>
       </c>
       <c r="B580" t="s">
-        <v>2423</v>
+        <v>2422</v>
       </c>
       <c r="C580" t="s">
         <v>721</v>
@@ -23522,16 +23522,16 @@
     </row>
     <row r="581" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B581" t="s">
+        <v>2406</v>
+      </c>
+      <c r="C581" t="s">
+        <v>721</v>
+      </c>
+      <c r="D581" s="6" t="s">
         <v>2405</v>
-      </c>
-      <c r="B581" t="s">
-        <v>2407</v>
-      </c>
-      <c r="C581" t="s">
-        <v>721</v>
-      </c>
-      <c r="D581" s="6" t="s">
-        <v>2406</v>
       </c>
       <c r="E581" s="4" t="s">
         <v>721</v>
@@ -23545,10 +23545,10 @@
     </row>
     <row r="582" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
       <c r="B582" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="C582" t="s">
         <v>721</v>
@@ -23571,10 +23571,10 @@
     </row>
     <row r="583" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="B583" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="C583" t="s">
         <v>721</v>
@@ -23591,16 +23591,16 @@
     </row>
     <row r="584" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
+        <v>2492</v>
+      </c>
+      <c r="B584" t="s">
+        <v>2493</v>
+      </c>
+      <c r="C584" t="s">
+        <v>721</v>
+      </c>
+      <c r="D584" s="6" t="s">
         <v>2494</v>
-      </c>
-      <c r="B584" t="s">
-        <v>2495</v>
-      </c>
-      <c r="C584" t="s">
-        <v>721</v>
-      </c>
-      <c r="D584" s="6" t="s">
-        <v>2496</v>
       </c>
       <c r="E584" s="4" t="s">
         <v>721</v>
@@ -23614,16 +23614,16 @@
     </row>
     <row r="585" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="B585" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="C585" t="s">
         <v>721</v>
       </c>
       <c r="D585" s="6" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="E585" s="4" t="s">
         <v>721</v>
@@ -23637,16 +23637,16 @@
     </row>
     <row r="586" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="B586" t="s">
-        <v>2503</v>
+        <v>2501</v>
       </c>
       <c r="C586" t="s">
         <v>721</v>
       </c>
       <c r="D586" s="6" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="E586" s="4" t="s">
         <v>721</v>
@@ -23660,16 +23660,16 @@
     </row>
     <row r="587" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="B587" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="C587" t="s">
         <v>721</v>
       </c>
       <c r="D587" s="6" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="E587" s="4" t="s">
         <v>721</v>
@@ -23683,16 +23683,16 @@
     </row>
     <row r="588" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="B588" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="C588" t="s">
         <v>721</v>
       </c>
       <c r="D588" s="6" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="E588" s="4" t="s">
         <v>721</v>
@@ -23706,16 +23706,16 @@
     </row>
     <row r="589" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="B589" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="C589" t="s">
         <v>721</v>
       </c>
       <c r="D589" s="6" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="E589" s="4" t="s">
         <v>721</v>
@@ -23824,7 +23824,7 @@
         <v>721</v>
       </c>
       <c r="D594" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="E594" s="4" t="s">
         <v>721</v>
@@ -24022,16 +24022,16 @@
     </row>
     <row r="603" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B603" t="s">
         <v>2408</v>
       </c>
-      <c r="B603" t="s">
+      <c r="C603" t="s">
+        <v>721</v>
+      </c>
+      <c r="D603" s="6" t="s">
         <v>2409</v>
-      </c>
-      <c r="C603" t="s">
-        <v>721</v>
-      </c>
-      <c r="D603" s="6" t="s">
-        <v>2410</v>
       </c>
       <c r="E603" s="4" t="s">
         <v>721</v>
@@ -24045,16 +24045,16 @@
     </row>
     <row r="604" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
+        <v>2410</v>
+      </c>
+      <c r="B604" t="s">
         <v>2411</v>
       </c>
-      <c r="B604" t="s">
+      <c r="C604" t="s">
+        <v>721</v>
+      </c>
+      <c r="D604" s="6" t="s">
         <v>2412</v>
-      </c>
-      <c r="C604" t="s">
-        <v>721</v>
-      </c>
-      <c r="D604" s="6" t="s">
-        <v>2413</v>
       </c>
       <c r="E604" s="4" t="s">
         <v>721</v>
@@ -24151,16 +24151,16 @@
     </row>
     <row r="609" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B609" t="s">
         <v>2414</v>
       </c>
-      <c r="B609" t="s">
+      <c r="C609" t="s">
+        <v>721</v>
+      </c>
+      <c r="D609" s="6" t="s">
         <v>2415</v>
-      </c>
-      <c r="C609" t="s">
-        <v>721</v>
-      </c>
-      <c r="D609" s="6" t="s">
-        <v>2416</v>
       </c>
       <c r="E609" s="4" t="s">
         <v>721</v>
@@ -24174,10 +24174,10 @@
     </row>
     <row r="610" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="B610" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="C610" t="s">
         <v>721</v>
@@ -24200,16 +24200,16 @@
     </row>
     <row r="611" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B611" t="s">
         <v>2417</v>
       </c>
-      <c r="B611" t="s">
+      <c r="C611" t="s">
+        <v>721</v>
+      </c>
+      <c r="D611" s="6" t="s">
         <v>2418</v>
-      </c>
-      <c r="C611" t="s">
-        <v>721</v>
-      </c>
-      <c r="D611" s="6" t="s">
-        <v>2419</v>
       </c>
       <c r="E611" s="4" t="s">
         <v>721</v>
@@ -24226,7 +24226,7 @@
         <v>1760</v>
       </c>
       <c r="B612" t="s">
-        <v>2424</v>
+        <v>2423</v>
       </c>
       <c r="C612" t="s">
         <v>721</v>
@@ -24246,7 +24246,7 @@
         <v>1761</v>
       </c>
       <c r="B613" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="C613" t="s">
         <v>721</v>
@@ -24272,7 +24272,7 @@
         <v>1604</v>
       </c>
       <c r="B614" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="C614" t="s">
         <v>721</v>
@@ -24298,7 +24298,7 @@
         <v>1605</v>
       </c>
       <c r="B615" t="s">
-        <v>2427</v>
+        <v>2426</v>
       </c>
       <c r="C615" t="s">
         <v>721</v>
@@ -24321,7 +24321,7 @@
         <v>1588</v>
       </c>
       <c r="B616" t="s">
-        <v>2428</v>
+        <v>2427</v>
       </c>
       <c r="C616" t="s">
         <v>721</v>
@@ -24341,7 +24341,7 @@
         <v>1642</v>
       </c>
       <c r="B617" t="s">
-        <v>2429</v>
+        <v>2428</v>
       </c>
       <c r="C617" t="s">
         <v>721</v>
@@ -24361,16 +24361,16 @@
     </row>
     <row r="618" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B618" t="s">
         <v>2420</v>
       </c>
-      <c r="B618" t="s">
-        <v>2421</v>
-      </c>
       <c r="C618" t="s">
         <v>721</v>
       </c>
       <c r="D618" s="6" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="E618" s="4" t="s">
         <v>721</v>
@@ -24387,7 +24387,7 @@
         <v>1589</v>
       </c>
       <c r="B619" t="s">
-        <v>2430</v>
+        <v>2429</v>
       </c>
       <c r="C619" t="s">
         <v>721</v>
@@ -24407,7 +24407,7 @@
         <v>1591</v>
       </c>
       <c r="B620" t="s">
-        <v>2431</v>
+        <v>2430</v>
       </c>
       <c r="C620" t="s">
         <v>721</v>
@@ -24427,7 +24427,7 @@
         <v>1644</v>
       </c>
       <c r="B621" t="s">
-        <v>2432</v>
+        <v>2431</v>
       </c>
       <c r="C621" t="s">
         <v>721</v>
@@ -24447,16 +24447,16 @@
     </row>
     <row r="622" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B622" t="s">
         <v>2434</v>
       </c>
-      <c r="B622" t="s">
-        <v>2435</v>
-      </c>
       <c r="C622" t="s">
         <v>721</v>
       </c>
       <c r="D622" s="6" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="E622" s="4" t="s">
         <v>721</v>
@@ -24473,7 +24473,7 @@
         <v>1592</v>
       </c>
       <c r="B623" t="s">
-        <v>2433</v>
+        <v>2432</v>
       </c>
       <c r="C623" t="s">
         <v>721</v>
@@ -24570,16 +24570,16 @@
     </row>
     <row r="628" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B628" t="s">
         <v>2436</v>
       </c>
-      <c r="B628" t="s">
+      <c r="C628" t="s">
+        <v>721</v>
+      </c>
+      <c r="D628" s="6" t="s">
         <v>2437</v>
-      </c>
-      <c r="C628" t="s">
-        <v>721</v>
-      </c>
-      <c r="D628" s="6" t="s">
-        <v>2438</v>
       </c>
       <c r="E628" s="4" t="s">
         <v>721</v>
@@ -24633,16 +24633,16 @@
     </row>
     <row r="631" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B631" t="s">
         <v>2439</v>
       </c>
-      <c r="B631" t="s">
-        <v>2440</v>
-      </c>
       <c r="C631" t="s">
         <v>721</v>
       </c>
       <c r="D631" s="6" t="s">
-        <v>2438</v>
+        <v>2437</v>
       </c>
       <c r="E631" s="4" t="s">
         <v>721</v>
@@ -24871,30 +24871,30 @@
     </row>
     <row r="644" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B644" t="s">
         <v>2755</v>
       </c>
-      <c r="B644" t="s">
-        <v>2757</v>
-      </c>
       <c r="C644" t="s">
         <v>721</v>
       </c>
       <c r="D644" t="s">
+        <v>2754</v>
+      </c>
+      <c r="H644" s="3" t="s">
         <v>2756</v>
       </c>
-      <c r="H644" s="3" t="s">
-        <v>2758</v>
-      </c>
       <c r="I644" s="3" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="645" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B645" t="s">
         <v>2443</v>
-      </c>
-      <c r="B645" t="s">
-        <v>2444</v>
       </c>
       <c r="C645" t="s">
         <v>721</v>
@@ -24925,10 +24925,10 @@
     </row>
     <row r="648" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
       <c r="B648" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="C648" t="s">
         <v>721</v>
@@ -24948,10 +24948,10 @@
     </row>
     <row r="649" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="B649" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="C649" t="s">
         <v>721</v>
@@ -25425,10 +25425,10 @@
     </row>
     <row r="671" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B671" t="s">
         <v>2050</v>
-      </c>
-      <c r="B671" t="s">
-        <v>2051</v>
       </c>
       <c r="C671" t="s">
         <v>721</v>
@@ -25808,16 +25808,16 @@
     </row>
     <row r="688" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B688" t="s">
         <v>2205</v>
       </c>
-      <c r="B688" t="s">
+      <c r="C688" t="s">
+        <v>721</v>
+      </c>
+      <c r="D688" t="s">
         <v>2206</v>
-      </c>
-      <c r="C688" t="s">
-        <v>721</v>
-      </c>
-      <c r="D688" t="s">
-        <v>2207</v>
       </c>
       <c r="E688" s="4" t="s">
         <v>721</v>
@@ -25825,16 +25825,16 @@
     </row>
     <row r="689" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B689" t="s">
         <v>2201</v>
       </c>
-      <c r="B689" t="s">
-        <v>2202</v>
-      </c>
       <c r="C689" t="s">
         <v>721</v>
       </c>
       <c r="D689" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="E689" s="4" t="s">
         <v>721</v>
@@ -25842,10 +25842,10 @@
     </row>
     <row r="690" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B690" t="s">
         <v>2198</v>
-      </c>
-      <c r="B690" t="s">
-        <v>2199</v>
       </c>
       <c r="C690" t="s">
         <v>721</v>
@@ -25862,16 +25862,16 @@
     </row>
     <row r="691" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B691" t="s">
         <v>2203</v>
       </c>
-      <c r="B691" t="s">
-        <v>2204</v>
-      </c>
       <c r="C691" t="s">
         <v>721</v>
       </c>
       <c r="D691" t="s">
-        <v>2705</v>
+        <v>2703</v>
       </c>
       <c r="E691" s="4" t="s">
         <v>721</v>
@@ -25879,10 +25879,10 @@
     </row>
     <row r="692" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="B692" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="C692" t="s">
         <v>721</v>
@@ -25951,10 +25951,10 @@
     </row>
     <row r="695" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B695" t="s">
         <v>2101</v>
-      </c>
-      <c r="B695" t="s">
-        <v>2102</v>
       </c>
       <c r="C695" t="s">
         <v>721</v>
@@ -26055,10 +26055,10 @@
     </row>
     <row r="699" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B699" t="s">
         <v>2099</v>
-      </c>
-      <c r="B699" t="s">
-        <v>2100</v>
       </c>
       <c r="C699" t="s">
         <v>721</v>
@@ -26090,7 +26090,7 @@
         <v>721</v>
       </c>
       <c r="D701" s="6" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="E701" s="4" t="s">
         <v>721</v>
@@ -26107,7 +26107,7 @@
         <v>1189</v>
       </c>
       <c r="B702" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="C702" t="s">
         <v>721</v>
@@ -26165,7 +26165,7 @@
         <v>721</v>
       </c>
       <c r="D704" t="s">
-        <v>2467</v>
+        <v>2465</v>
       </c>
       <c r="E704" s="4" t="s">
         <v>721</v>
@@ -26254,10 +26254,10 @@
     </row>
     <row r="709" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
       <c r="B709" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="D709" t="s">
         <v>128</v>
@@ -26271,13 +26271,13 @@
     </row>
     <row r="710" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B710" t="s">
         <v>2464</v>
       </c>
-      <c r="B710" t="s">
+      <c r="D710" t="s">
         <v>2466</v>
-      </c>
-      <c r="D710" t="s">
-        <v>2468</v>
       </c>
       <c r="E710" s="4" t="s">
         <v>721</v>
@@ -26288,7 +26288,7 @@
         <v>166</v>
       </c>
       <c r="B711" t="s">
-        <v>2465</v>
+        <v>2463</v>
       </c>
       <c r="C711" t="s">
         <v>721</v>
@@ -26640,10 +26640,10 @@
     </row>
     <row r="726" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B726" t="s">
         <v>2452</v>
-      </c>
-      <c r="B726" t="s">
-        <v>2453</v>
       </c>
       <c r="C726" t="s">
         <v>721</v>
@@ -26718,16 +26718,16 @@
     </row>
     <row r="730" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B730" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="C730" t="s">
         <v>721</v>
       </c>
       <c r="D730" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="E730" s="4" t="s">
         <v>721</v>
@@ -26735,16 +26735,16 @@
     </row>
     <row r="731" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
       <c r="B731" t="s">
-        <v>2212</v>
+        <v>2211</v>
       </c>
       <c r="C731" t="s">
         <v>721</v>
       </c>
       <c r="D731" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
       <c r="E731" s="4" t="s">
         <v>721</v>
@@ -27129,7 +27129,7 @@
         <v>711</v>
       </c>
       <c r="B750" t="s">
-        <v>2076</v>
+        <v>2075</v>
       </c>
       <c r="C750" t="s">
         <v>721</v>
@@ -27158,7 +27158,7 @@
         <v>688</v>
       </c>
       <c r="E751" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F751" s="4" t="s">
         <v>689</v>
@@ -27175,7 +27175,7 @@
         <v>1894</v>
       </c>
       <c r="B752" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="C752" t="s">
         <v>721</v>
@@ -27184,7 +27184,7 @@
         <v>688</v>
       </c>
       <c r="E752" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F752" s="4" t="s">
         <v>689</v>
@@ -27201,7 +27201,7 @@
         <v>1895</v>
       </c>
       <c r="B753" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="C753" t="s">
         <v>721</v>
@@ -27210,7 +27210,7 @@
         <v>688</v>
       </c>
       <c r="E753" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F753" s="4" t="s">
         <v>689</v>
@@ -27227,7 +27227,7 @@
         <v>1870</v>
       </c>
       <c r="B754" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="C754" t="s">
         <v>721</v>
@@ -27236,7 +27236,7 @@
         <v>688</v>
       </c>
       <c r="E754" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F754" s="4" t="s">
         <v>689</v>
@@ -27253,7 +27253,7 @@
         <v>1871</v>
       </c>
       <c r="B755" t="s">
-        <v>2288</v>
+        <v>2287</v>
       </c>
       <c r="C755" t="s">
         <v>721</v>
@@ -27262,7 +27262,7 @@
         <v>688</v>
       </c>
       <c r="E755" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F755" s="4" t="s">
         <v>689</v>
@@ -27279,7 +27279,7 @@
         <v>1876</v>
       </c>
       <c r="B756" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="C756" t="s">
         <v>721</v>
@@ -27288,7 +27288,7 @@
         <v>688</v>
       </c>
       <c r="E756" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F756" s="4" t="s">
         <v>689</v>
@@ -27305,7 +27305,7 @@
         <v>1877</v>
       </c>
       <c r="B757" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="C757" t="s">
         <v>721</v>
@@ -27314,7 +27314,7 @@
         <v>688</v>
       </c>
       <c r="E757" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F757" s="4" t="s">
         <v>689</v>
@@ -27331,7 +27331,7 @@
         <v>720</v>
       </c>
       <c r="B758" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="C758" t="s">
         <v>721</v>
@@ -27340,7 +27340,7 @@
         <v>688</v>
       </c>
       <c r="E758" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F758" s="4" t="s">
         <v>689</v>
@@ -27357,7 +27357,7 @@
         <v>697</v>
       </c>
       <c r="B759" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="C759" t="s">
         <v>721</v>
@@ -27366,7 +27366,7 @@
         <v>688</v>
       </c>
       <c r="E759" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F759" s="4" t="s">
         <v>689</v>
@@ -27383,7 +27383,7 @@
         <v>1864</v>
       </c>
       <c r="B760" t="s">
-        <v>2293</v>
+        <v>2292</v>
       </c>
       <c r="C760" t="s">
         <v>721</v>
@@ -27392,7 +27392,7 @@
         <v>688</v>
       </c>
       <c r="E760" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F760" s="4" t="s">
         <v>689</v>
@@ -27406,7 +27406,7 @@
         <v>1865</v>
       </c>
       <c r="B761" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="C761" t="s">
         <v>721</v>
@@ -27415,7 +27415,7 @@
         <v>688</v>
       </c>
       <c r="E761" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F761" s="4" t="s">
         <v>689</v>
@@ -27429,7 +27429,7 @@
         <v>718</v>
       </c>
       <c r="B762" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="C762" t="s">
         <v>721</v>
@@ -27438,7 +27438,7 @@
         <v>688</v>
       </c>
       <c r="E762" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F762" s="4" t="s">
         <v>689</v>
@@ -27455,7 +27455,7 @@
         <v>695</v>
       </c>
       <c r="B763" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="C763" t="s">
         <v>721</v>
@@ -27464,7 +27464,7 @@
         <v>688</v>
       </c>
       <c r="E763" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F763" s="4" t="s">
         <v>689</v>
@@ -27481,7 +27481,7 @@
         <v>713</v>
       </c>
       <c r="B764" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="C764" t="s">
         <v>721</v>
@@ -27490,7 +27490,7 @@
         <v>688</v>
       </c>
       <c r="E764" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F764" s="4" t="s">
         <v>689</v>
@@ -27507,7 +27507,7 @@
         <v>690</v>
       </c>
       <c r="B765" t="s">
-        <v>2298</v>
+        <v>2297</v>
       </c>
       <c r="C765" t="s">
         <v>721</v>
@@ -27516,7 +27516,7 @@
         <v>688</v>
       </c>
       <c r="E765" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F765" s="4" t="s">
         <v>689</v>
@@ -27533,7 +27533,7 @@
         <v>714</v>
       </c>
       <c r="B766" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="C766" t="s">
         <v>721</v>
@@ -27542,7 +27542,7 @@
         <v>688</v>
       </c>
       <c r="E766" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F766" s="4" t="s">
         <v>689</v>
@@ -27559,7 +27559,7 @@
         <v>691</v>
       </c>
       <c r="B767" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="C767" t="s">
         <v>721</v>
@@ -27568,7 +27568,7 @@
         <v>688</v>
       </c>
       <c r="E767" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F767" s="4" t="s">
         <v>689</v>
@@ -27585,7 +27585,7 @@
         <v>777</v>
       </c>
       <c r="B768" t="s">
-        <v>2301</v>
+        <v>2300</v>
       </c>
       <c r="C768" t="s">
         <v>721</v>
@@ -27594,7 +27594,7 @@
         <v>688</v>
       </c>
       <c r="E768" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F768" s="4" t="s">
         <v>689</v>
@@ -27608,7 +27608,7 @@
         <v>778</v>
       </c>
       <c r="B769" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="C769" t="s">
         <v>721</v>
@@ -27617,7 +27617,7 @@
         <v>688</v>
       </c>
       <c r="E769" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F769" s="4" t="s">
         <v>689</v>
@@ -27631,7 +27631,7 @@
         <v>1859</v>
       </c>
       <c r="B770" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="C770" t="s">
         <v>721</v>
@@ -27640,7 +27640,7 @@
         <v>688</v>
       </c>
       <c r="E770" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F770" s="4" t="s">
         <v>689</v>
@@ -27654,7 +27654,7 @@
         <v>1519</v>
       </c>
       <c r="B771" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="C771" t="s">
         <v>721</v>
@@ -27663,7 +27663,7 @@
         <v>688</v>
       </c>
       <c r="E771" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F771" s="4" t="s">
         <v>689</v>
@@ -27680,7 +27680,7 @@
         <v>1880</v>
       </c>
       <c r="B772" t="s">
-        <v>2305</v>
+        <v>2304</v>
       </c>
       <c r="C772" t="s">
         <v>721</v>
@@ -27689,7 +27689,7 @@
         <v>688</v>
       </c>
       <c r="E772" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F772" s="4" t="s">
         <v>689</v>
@@ -27706,7 +27706,7 @@
         <v>1881</v>
       </c>
       <c r="B773" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="C773" t="s">
         <v>721</v>
@@ -27715,7 +27715,7 @@
         <v>688</v>
       </c>
       <c r="E773" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F773" s="4" t="s">
         <v>689</v>
@@ -27732,7 +27732,7 @@
         <v>1888</v>
       </c>
       <c r="B774" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="C774" t="s">
         <v>721</v>
@@ -27741,7 +27741,7 @@
         <v>688</v>
       </c>
       <c r="E774" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F774" s="4" t="s">
         <v>689</v>
@@ -27758,7 +27758,7 @@
         <v>1889</v>
       </c>
       <c r="B775" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="C775" t="s">
         <v>721</v>
@@ -27767,7 +27767,7 @@
         <v>688</v>
       </c>
       <c r="E775" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F775" s="4" t="s">
         <v>689</v>
@@ -27784,7 +27784,7 @@
         <v>1890</v>
       </c>
       <c r="B776" t="s">
-        <v>2309</v>
+        <v>2308</v>
       </c>
       <c r="C776" t="s">
         <v>721</v>
@@ -27793,7 +27793,7 @@
         <v>688</v>
       </c>
       <c r="E776" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F776" s="4" t="s">
         <v>689</v>
@@ -27810,7 +27810,7 @@
         <v>1891</v>
       </c>
       <c r="B777" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="C777" t="s">
         <v>721</v>
@@ -27819,7 +27819,7 @@
         <v>688</v>
       </c>
       <c r="E777" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F777" s="4" t="s">
         <v>689</v>
@@ -27836,7 +27836,7 @@
         <v>1892</v>
       </c>
       <c r="B778" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="C778" t="s">
         <v>721</v>
@@ -27845,7 +27845,7 @@
         <v>688</v>
       </c>
       <c r="E778" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F778" s="4" t="s">
         <v>689</v>
@@ -27862,7 +27862,7 @@
         <v>1893</v>
       </c>
       <c r="B779" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="C779" t="s">
         <v>721</v>
@@ -27871,7 +27871,7 @@
         <v>688</v>
       </c>
       <c r="E779" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F779" s="4" t="s">
         <v>689</v>
@@ -27888,7 +27888,7 @@
         <v>1874</v>
       </c>
       <c r="B780" t="s">
-        <v>2313</v>
+        <v>2312</v>
       </c>
       <c r="C780" t="s">
         <v>721</v>
@@ -27897,7 +27897,7 @@
         <v>688</v>
       </c>
       <c r="E780" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F780" s="4" t="s">
         <v>689</v>
@@ -27914,7 +27914,7 @@
         <v>1875</v>
       </c>
       <c r="B781" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="C781" t="s">
         <v>721</v>
@@ -27923,7 +27923,7 @@
         <v>688</v>
       </c>
       <c r="E781" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F781" s="4" t="s">
         <v>689</v>
@@ -27940,7 +27940,7 @@
         <v>715</v>
       </c>
       <c r="B782" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="C782" t="s">
         <v>721</v>
@@ -27949,7 +27949,7 @@
         <v>688</v>
       </c>
       <c r="E782" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F782" s="4" t="s">
         <v>689</v>
@@ -27966,7 +27966,7 @@
         <v>692</v>
       </c>
       <c r="B783" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="C783" t="s">
         <v>721</v>
@@ -27975,7 +27975,7 @@
         <v>688</v>
       </c>
       <c r="E783" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F783" s="4" t="s">
         <v>689</v>
@@ -27992,7 +27992,7 @@
         <v>1872</v>
       </c>
       <c r="B784" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="C784" t="s">
         <v>721</v>
@@ -28001,7 +28001,7 @@
         <v>688</v>
       </c>
       <c r="E784" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F784" s="4" t="s">
         <v>689</v>
@@ -28018,7 +28018,7 @@
         <v>1873</v>
       </c>
       <c r="B785" t="s">
-        <v>2318</v>
+        <v>2317</v>
       </c>
       <c r="C785" t="s">
         <v>721</v>
@@ -28027,7 +28027,7 @@
         <v>688</v>
       </c>
       <c r="E785" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F785" s="4" t="s">
         <v>689</v>
@@ -28044,7 +28044,7 @@
         <v>717</v>
       </c>
       <c r="B786" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="C786" t="s">
         <v>721</v>
@@ -28053,7 +28053,7 @@
         <v>688</v>
       </c>
       <c r="E786" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F786" s="4" t="s">
         <v>689</v>
@@ -28070,7 +28070,7 @@
         <v>694</v>
       </c>
       <c r="B787" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="C787" t="s">
         <v>721</v>
@@ -28079,7 +28079,7 @@
         <v>688</v>
       </c>
       <c r="E787" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F787" s="4" t="s">
         <v>689</v>
@@ -28093,10 +28093,10 @@
     </row>
     <row r="788" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B788" t="s">
         <v>2052</v>
-      </c>
-      <c r="B788" t="s">
-        <v>2053</v>
       </c>
       <c r="C788" t="s">
         <v>721</v>
@@ -28122,7 +28122,7 @@
         <v>1860</v>
       </c>
       <c r="B789" t="s">
-        <v>2321</v>
+        <v>2320</v>
       </c>
       <c r="C789" t="s">
         <v>721</v>
@@ -28131,7 +28131,7 @@
         <v>688</v>
       </c>
       <c r="E789" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F789" s="4" t="s">
         <v>689</v>
@@ -28145,7 +28145,7 @@
         <v>1861</v>
       </c>
       <c r="B790" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="C790" t="s">
         <v>721</v>
@@ -28154,7 +28154,7 @@
         <v>688</v>
       </c>
       <c r="E790" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F790" s="4" t="s">
         <v>689</v>
@@ -28168,7 +28168,7 @@
         <v>1862</v>
       </c>
       <c r="B791" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="C791" t="s">
         <v>721</v>
@@ -28177,7 +28177,7 @@
         <v>688</v>
       </c>
       <c r="E791" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F791" s="4" t="s">
         <v>689</v>
@@ -28191,7 +28191,7 @@
         <v>1863</v>
       </c>
       <c r="B792" t="s">
-        <v>2324</v>
+        <v>2323</v>
       </c>
       <c r="C792" t="s">
         <v>721</v>
@@ -28200,7 +28200,7 @@
         <v>688</v>
       </c>
       <c r="E792" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F792" s="4" t="s">
         <v>689</v>
@@ -28214,7 +28214,7 @@
         <v>712</v>
       </c>
       <c r="B793" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="C793" t="s">
         <v>721</v>
@@ -28223,7 +28223,7 @@
         <v>688</v>
       </c>
       <c r="E793" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F793" s="4" t="s">
         <v>689</v>
@@ -28240,7 +28240,7 @@
         <v>902</v>
       </c>
       <c r="B794" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="C794" t="s">
         <v>721</v>
@@ -28249,7 +28249,7 @@
         <v>688</v>
       </c>
       <c r="E794" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F794" s="4" t="s">
         <v>689</v>
@@ -28266,7 +28266,7 @@
         <v>1884</v>
       </c>
       <c r="B795" t="s">
-        <v>2327</v>
+        <v>2326</v>
       </c>
       <c r="C795" t="s">
         <v>721</v>
@@ -28275,7 +28275,7 @@
         <v>688</v>
       </c>
       <c r="E795" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F795" s="4" t="s">
         <v>689</v>
@@ -28292,7 +28292,7 @@
         <v>1885</v>
       </c>
       <c r="B796" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="C796" t="s">
         <v>721</v>
@@ -28301,7 +28301,7 @@
         <v>688</v>
       </c>
       <c r="E796" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F796" s="4" t="s">
         <v>689</v>
@@ -28318,7 +28318,7 @@
         <v>719</v>
       </c>
       <c r="B797" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="C797" t="s">
         <v>721</v>
@@ -28327,7 +28327,7 @@
         <v>688</v>
       </c>
       <c r="E797" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F797" s="4" t="s">
         <v>689</v>
@@ -28344,7 +28344,7 @@
         <v>696</v>
       </c>
       <c r="B798" t="s">
-        <v>2330</v>
+        <v>2329</v>
       </c>
       <c r="C798" t="s">
         <v>721</v>
@@ -28353,7 +28353,7 @@
         <v>688</v>
       </c>
       <c r="E798" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F798" s="4" t="s">
         <v>689</v>
@@ -28370,7 +28370,7 @@
         <v>1896</v>
       </c>
       <c r="B799" t="s">
-        <v>2331</v>
+        <v>2330</v>
       </c>
       <c r="C799" t="s">
         <v>721</v>
@@ -28379,7 +28379,7 @@
         <v>688</v>
       </c>
       <c r="E799" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F799" s="4" t="s">
         <v>689</v>
@@ -28393,7 +28393,7 @@
         <v>1897</v>
       </c>
       <c r="B800" t="s">
-        <v>2332</v>
+        <v>2331</v>
       </c>
       <c r="C800" t="s">
         <v>721</v>
@@ -28402,7 +28402,7 @@
         <v>688</v>
       </c>
       <c r="E800" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F800" s="4" t="s">
         <v>689</v>
@@ -28416,7 +28416,7 @@
         <v>1882</v>
       </c>
       <c r="B801" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="C801" t="s">
         <v>721</v>
@@ -28425,7 +28425,7 @@
         <v>688</v>
       </c>
       <c r="E801" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F801" s="4" t="s">
         <v>689</v>
@@ -28442,7 +28442,7 @@
         <v>1883</v>
       </c>
       <c r="B802" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="C802" t="s">
         <v>721</v>
@@ -28451,7 +28451,7 @@
         <v>688</v>
       </c>
       <c r="E802" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F802" s="4" t="s">
         <v>689</v>
@@ -28468,7 +28468,7 @@
         <v>1878</v>
       </c>
       <c r="B803" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="C803" t="s">
         <v>721</v>
@@ -28477,7 +28477,7 @@
         <v>688</v>
       </c>
       <c r="E803" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F803" s="4" t="s">
         <v>689</v>
@@ -28494,7 +28494,7 @@
         <v>1879</v>
       </c>
       <c r="B804" t="s">
-        <v>2336</v>
+        <v>2335</v>
       </c>
       <c r="C804" t="s">
         <v>721</v>
@@ -28503,7 +28503,7 @@
         <v>688</v>
       </c>
       <c r="E804" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F804" s="4" t="s">
         <v>689</v>
@@ -28520,7 +28520,7 @@
         <v>1886</v>
       </c>
       <c r="B805" t="s">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="C805" t="s">
         <v>721</v>
@@ -28529,7 +28529,7 @@
         <v>688</v>
       </c>
       <c r="E805" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F805" s="4" t="s">
         <v>689</v>
@@ -28543,7 +28543,7 @@
         <v>1887</v>
       </c>
       <c r="B806" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="C806" t="s">
         <v>721</v>
@@ -28552,7 +28552,7 @@
         <v>688</v>
       </c>
       <c r="E806" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F806" s="4" t="s">
         <v>689</v>
@@ -28566,7 +28566,7 @@
         <v>1868</v>
       </c>
       <c r="B807" t="s">
-        <v>2339</v>
+        <v>2338</v>
       </c>
       <c r="C807" t="s">
         <v>721</v>
@@ -28575,7 +28575,7 @@
         <v>688</v>
       </c>
       <c r="E807" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F807" s="4" t="s">
         <v>689</v>
@@ -28592,7 +28592,7 @@
         <v>1869</v>
       </c>
       <c r="B808" t="s">
-        <v>2340</v>
+        <v>2339</v>
       </c>
       <c r="C808" t="s">
         <v>721</v>
@@ -28601,7 +28601,7 @@
         <v>688</v>
       </c>
       <c r="E808" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F808" s="4" t="s">
         <v>689</v>
@@ -28618,7 +28618,7 @@
         <v>716</v>
       </c>
       <c r="B809" t="s">
-        <v>2341</v>
+        <v>2340</v>
       </c>
       <c r="C809" t="s">
         <v>721</v>
@@ -28627,7 +28627,7 @@
         <v>688</v>
       </c>
       <c r="E809" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F809" s="4" t="s">
         <v>689</v>
@@ -28644,7 +28644,7 @@
         <v>693</v>
       </c>
       <c r="B810" t="s">
-        <v>2342</v>
+        <v>2341</v>
       </c>
       <c r="C810" t="s">
         <v>721</v>
@@ -28653,7 +28653,7 @@
         <v>688</v>
       </c>
       <c r="E810" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F810" s="4" t="s">
         <v>689</v>
@@ -28670,7 +28670,7 @@
         <v>1866</v>
       </c>
       <c r="B811" t="s">
-        <v>2343</v>
+        <v>2342</v>
       </c>
       <c r="C811" t="s">
         <v>721</v>
@@ -28679,7 +28679,7 @@
         <v>688</v>
       </c>
       <c r="E811" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F811" s="4" t="s">
         <v>689</v>
@@ -28696,7 +28696,7 @@
         <v>1867</v>
       </c>
       <c r="B812" t="s">
-        <v>2344</v>
+        <v>2343</v>
       </c>
       <c r="C812" t="s">
         <v>721</v>
@@ -28705,7 +28705,7 @@
         <v>688</v>
       </c>
       <c r="E812" s="4" t="s">
-        <v>2284</v>
+        <v>2283</v>
       </c>
       <c r="F812" s="4" t="s">
         <v>689</v>
@@ -28722,13 +28722,13 @@
         <v>1525</v>
       </c>
       <c r="B813" t="s">
-        <v>2345</v>
+        <v>2344</v>
       </c>
       <c r="C813" t="s">
         <v>721</v>
       </c>
       <c r="D813" t="s">
-        <v>2073</v>
+        <v>2072</v>
       </c>
       <c r="E813" s="4" t="s">
         <v>721</v>
@@ -28739,13 +28739,13 @@
         <v>1526</v>
       </c>
       <c r="B814" t="s">
-        <v>2346</v>
+        <v>2345</v>
       </c>
       <c r="C814" t="s">
         <v>721</v>
       </c>
       <c r="D814" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="E814" s="4" t="s">
         <v>721</v>
@@ -28762,7 +28762,7 @@
         <v>721</v>
       </c>
       <c r="D815" t="s">
-        <v>2357</v>
+        <v>2356</v>
       </c>
       <c r="E815" s="4" t="s">
         <v>721</v>
@@ -28779,7 +28779,7 @@
         <v>721</v>
       </c>
       <c r="D816" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="E816" s="4" t="s">
         <v>721</v>
@@ -30210,16 +30210,16 @@
     </row>
     <row r="881" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B881" t="s">
         <v>2387</v>
       </c>
-      <c r="B881" t="s">
+      <c r="C881" t="s">
+        <v>721</v>
+      </c>
+      <c r="D881" t="s">
         <v>2388</v>
-      </c>
-      <c r="C881" t="s">
-        <v>721</v>
-      </c>
-      <c r="D881" t="s">
-        <v>2389</v>
       </c>
     </row>
     <row r="882" spans="1:9" x14ac:dyDescent="0.25">
@@ -30384,10 +30384,10 @@
     </row>
     <row r="890" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B890" t="s">
         <v>2378</v>
-      </c>
-      <c r="B890" t="s">
-        <v>2379</v>
       </c>
       <c r="C890" t="s">
         <v>721</v>
@@ -30430,10 +30430,10 @@
     </row>
     <row r="892" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B892" t="s">
         <v>2140</v>
-      </c>
-      <c r="B892" t="s">
-        <v>2141</v>
       </c>
       <c r="C892" t="s">
         <v>721</v>
@@ -30588,10 +30588,10 @@
     </row>
     <row r="899" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
       <c r="B899" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="C899" t="s">
         <v>721</v>
@@ -30648,10 +30648,10 @@
     </row>
     <row r="902" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B902" t="s">
         <v>2237</v>
-      </c>
-      <c r="B902" t="s">
-        <v>2238</v>
       </c>
       <c r="C902" t="s">
         <v>721</v>
@@ -31106,10 +31106,10 @@
     </row>
     <row r="921" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
       <c r="B921" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="C921" t="s">
         <v>721</v>
@@ -31126,10 +31126,10 @@
     </row>
     <row r="922" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
       <c r="B922" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="C922" t="s">
         <v>721</v>
@@ -31152,10 +31152,10 @@
     </row>
     <row r="923" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="B923" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="C923" t="s">
         <v>721</v>
@@ -31175,10 +31175,10 @@
     </row>
     <row r="924" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="B924" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="C924" t="s">
         <v>721</v>
@@ -31195,10 +31195,10 @@
     </row>
     <row r="925" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="B925" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="C925" t="s">
         <v>721</v>
@@ -31221,10 +31221,10 @@
     </row>
     <row r="926" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="B926" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="C926" t="s">
         <v>721</v>
@@ -31365,7 +31365,7 @@
         <v>867</v>
       </c>
       <c r="B932" t="s">
-        <v>2382</v>
+        <v>2381</v>
       </c>
       <c r="C932" t="s">
         <v>721</v>
@@ -31649,10 +31649,10 @@
     </row>
     <row r="945" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B945" t="s">
         <v>2239</v>
-      </c>
-      <c r="B945" t="s">
-        <v>2240</v>
       </c>
       <c r="C945" t="s">
         <v>721</v>
@@ -31669,10 +31669,10 @@
     </row>
     <row r="946" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B946" t="s">
         <v>2241</v>
-      </c>
-      <c r="B946" t="s">
-        <v>2242</v>
       </c>
       <c r="C946" t="s">
         <v>721</v>
@@ -31689,25 +31689,25 @@
     </row>
     <row r="947" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B947" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C947" t="s">
+        <v>721</v>
+      </c>
+      <c r="D947" t="s">
         <v>2148</v>
       </c>
-      <c r="B947" t="s">
-        <v>2151</v>
-      </c>
-      <c r="C947" t="s">
-        <v>721</v>
-      </c>
-      <c r="D947" t="s">
+      <c r="E947" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="H947" s="2" t="s">
         <v>2149</v>
       </c>
-      <c r="E947" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="H947" s="2" t="s">
-        <v>2150</v>
-      </c>
       <c r="I947" s="2" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
     </row>
     <row r="948" spans="1:9" x14ac:dyDescent="0.25">
@@ -31870,16 +31870,16 @@
     </row>
     <row r="955" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B955" t="s">
+        <v>2706</v>
+      </c>
+      <c r="C955" t="s">
+        <v>721</v>
+      </c>
+      <c r="D955" t="s">
         <v>2707</v>
-      </c>
-      <c r="B955" t="s">
-        <v>2708</v>
-      </c>
-      <c r="C955" t="s">
-        <v>721</v>
-      </c>
-      <c r="D955" t="s">
-        <v>2709</v>
       </c>
       <c r="E955" s="4" t="s">
         <v>721</v>
@@ -31893,10 +31893,10 @@
     </row>
     <row r="956" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B956" t="s">
         <v>2230</v>
-      </c>
-      <c r="B956" t="s">
-        <v>2231</v>
       </c>
       <c r="C956" t="s">
         <v>721</v>
@@ -31939,7 +31939,7 @@
     </row>
     <row r="958" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B958" t="s">
         <v>1980</v>
@@ -31959,7 +31959,7 @@
     </row>
     <row r="959" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B959" t="s">
         <v>1982</v>
@@ -32008,13 +32008,13 @@
         <v>151</v>
       </c>
       <c r="B961" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C961" t="s">
+        <v>721</v>
+      </c>
+      <c r="D961" t="s">
         <v>2089</v>
-      </c>
-      <c r="C961" t="s">
-        <v>721</v>
-      </c>
-      <c r="D961" t="s">
-        <v>2090</v>
       </c>
       <c r="E961" s="4" t="s">
         <v>721</v>
@@ -32031,13 +32031,13 @@
         <v>1845</v>
       </c>
       <c r="B962" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
       <c r="C962" t="s">
         <v>721</v>
       </c>
       <c r="D962" s="6" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="E962" s="4" t="s">
         <v>721</v>
@@ -32091,16 +32091,16 @@
     </row>
     <row r="965" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B965" t="s">
+        <v>2346</v>
+      </c>
+      <c r="C965" t="s">
+        <v>721</v>
+      </c>
+      <c r="D965" t="s">
         <v>2172</v>
-      </c>
-      <c r="B965" t="s">
-        <v>2347</v>
-      </c>
-      <c r="C965" t="s">
-        <v>721</v>
-      </c>
-      <c r="D965" t="s">
-        <v>2173</v>
       </c>
       <c r="E965" s="4" t="s">
         <v>142</v>
@@ -32140,7 +32140,7 @@
         <v>732</v>
       </c>
       <c r="B967" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="C967" t="s">
         <v>721</v>
@@ -32157,10 +32157,10 @@
     </row>
     <row r="968" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="B968" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="C968" t="s">
         <v>721</v>
@@ -32237,16 +32237,16 @@
     </row>
     <row r="972" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
       <c r="B972" t="s">
-        <v>2362</v>
+        <v>2361</v>
       </c>
       <c r="C972" t="s">
         <v>721</v>
       </c>
       <c r="D972" t="s">
-        <v>2360</v>
+        <v>2359</v>
       </c>
       <c r="E972" s="4" t="s">
         <v>721</v>
@@ -32260,16 +32260,16 @@
     </row>
     <row r="973" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B973" t="s">
+        <v>2360</v>
+      </c>
+      <c r="C973" t="s">
+        <v>721</v>
+      </c>
+      <c r="D973" t="s">
         <v>2359</v>
-      </c>
-      <c r="B973" t="s">
-        <v>2361</v>
-      </c>
-      <c r="C973" t="s">
-        <v>721</v>
-      </c>
-      <c r="D973" t="s">
-        <v>2360</v>
       </c>
       <c r="E973" s="4" t="s">
         <v>721</v>
@@ -32303,16 +32303,16 @@
     </row>
     <row r="976" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B976" t="s">
+        <v>2576</v>
+      </c>
+      <c r="C976" t="s">
+        <v>721</v>
+      </c>
+      <c r="D976" s="6" t="s">
         <v>2577</v>
-      </c>
-      <c r="B976" t="s">
-        <v>2578</v>
-      </c>
-      <c r="C976" t="s">
-        <v>721</v>
-      </c>
-      <c r="D976" s="6" t="s">
-        <v>2579</v>
       </c>
       <c r="E976" s="4" t="s">
         <v>721</v>
@@ -32326,10 +32326,10 @@
     </row>
     <row r="977" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
       <c r="B977" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="C977" t="s">
         <v>721</v>
@@ -32352,10 +32352,10 @@
     </row>
     <row r="978" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="B978" t="s">
-        <v>2613</v>
+        <v>2611</v>
       </c>
       <c r="C978" t="s">
         <v>721</v>
@@ -32378,16 +32378,16 @@
     </row>
     <row r="979" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B979" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C979" t="s">
+        <v>721</v>
+      </c>
+      <c r="D979" s="6" t="s">
         <v>2614</v>
-      </c>
-      <c r="B979" t="s">
-        <v>2615</v>
-      </c>
-      <c r="C979" t="s">
-        <v>721</v>
-      </c>
-      <c r="D979" s="6" t="s">
-        <v>2616</v>
       </c>
       <c r="E979" s="4" t="s">
         <v>721</v>
@@ -32401,10 +32401,10 @@
     </row>
     <row r="980" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="B980" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="C980" t="s">
         <v>721</v>
@@ -32424,10 +32424,10 @@
     </row>
     <row r="981" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
       <c r="B981" t="s">
-        <v>2659</v>
+        <v>2657</v>
       </c>
       <c r="C981" t="s">
         <v>721</v>
@@ -32444,10 +32444,10 @@
     </row>
     <row r="982" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="B982" t="s">
-        <v>2660</v>
+        <v>2658</v>
       </c>
       <c r="C982" t="s">
         <v>721</v>
@@ -32464,16 +32464,16 @@
     </row>
     <row r="983" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B983" t="s">
         <v>2652</v>
       </c>
-      <c r="B983" t="s">
-        <v>2654</v>
-      </c>
       <c r="C983" t="s">
         <v>721</v>
       </c>
       <c r="D983" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="E983" s="4" t="s">
         <v>721</v>
@@ -32481,10 +32481,10 @@
     </row>
     <row r="984" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="B984" t="s">
-        <v>2673</v>
+        <v>2671</v>
       </c>
       <c r="C984" t="s">
         <v>721</v>
@@ -32501,16 +32501,16 @@
     </row>
     <row r="985" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
+        <v>2651</v>
+      </c>
+      <c r="B985" t="s">
         <v>2653</v>
       </c>
-      <c r="B985" t="s">
-        <v>2655</v>
-      </c>
       <c r="C985" t="s">
         <v>721</v>
       </c>
       <c r="D985" t="s">
-        <v>2656</v>
+        <v>2654</v>
       </c>
       <c r="E985" s="4" t="s">
         <v>721</v>
@@ -32518,10 +32518,10 @@
     </row>
     <row r="986" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="B986" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="C986" t="s">
         <v>721</v>
@@ -32538,10 +32538,10 @@
     </row>
     <row r="987" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="B987" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="C987" t="s">
         <v>721</v>
@@ -32558,10 +32558,10 @@
     </row>
     <row r="988" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="B988" t="s">
-        <v>2581</v>
+        <v>2579</v>
       </c>
       <c r="C988" t="s">
         <v>721</v>
@@ -32578,10 +32578,10 @@
     </row>
     <row r="989" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="B989" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="C989" t="s">
         <v>721</v>
@@ -32604,10 +32604,10 @@
     </row>
     <row r="990" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="B990" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="C990" t="s">
         <v>721</v>
@@ -32630,10 +32630,10 @@
     </row>
     <row r="991" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
-        <v>2621</v>
+        <v>2619</v>
       </c>
       <c r="B991" t="s">
-        <v>2626</v>
+        <v>2624</v>
       </c>
       <c r="C991" t="s">
         <v>721</v>
@@ -32656,10 +32656,10 @@
     </row>
     <row r="992" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
       <c r="B992" t="s">
-        <v>2625</v>
+        <v>2623</v>
       </c>
       <c r="C992" t="s">
         <v>721</v>
@@ -32682,10 +32682,10 @@
     </row>
     <row r="993" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
       <c r="B993" t="s">
-        <v>2622</v>
+        <v>2620</v>
       </c>
       <c r="C993" t="s">
         <v>721</v>
@@ -32708,10 +32708,10 @@
     </row>
     <row r="994" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
-        <v>2620</v>
+        <v>2618</v>
       </c>
       <c r="B994" t="s">
-        <v>2623</v>
+        <v>2621</v>
       </c>
       <c r="C994" t="s">
         <v>721</v>
@@ -32734,10 +32734,10 @@
     </row>
     <row r="995" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="B995" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="C995" t="s">
         <v>721</v>
@@ -32760,10 +32760,10 @@
     </row>
     <row r="996" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="B996" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="C996" t="s">
         <v>721</v>
@@ -32786,10 +32786,10 @@
     </row>
     <row r="997" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="B997" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="C997" t="s">
         <v>721</v>
@@ -32812,10 +32812,10 @@
     </row>
     <row r="998" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="B998" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="C998" t="s">
         <v>721</v>
@@ -32838,10 +32838,10 @@
     </row>
     <row r="999" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
       <c r="B999" t="s">
-        <v>2601</v>
+        <v>2599</v>
       </c>
       <c r="C999" t="s">
         <v>721</v>
@@ -32864,10 +32864,10 @@
     </row>
     <row r="1000" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
       <c r="B1000" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="C1000" t="s">
         <v>721</v>
@@ -32890,10 +32890,10 @@
     </row>
     <row r="1001" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
       <c r="B1001" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="C1001" t="s">
         <v>721</v>
@@ -32908,18 +32908,18 @@
         <v>1247</v>
       </c>
       <c r="H1001" s="3" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
       <c r="I1001" s="3" t="s">
-        <v>2657</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="1002" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
       <c r="B1002" t="s">
-        <v>2628</v>
+        <v>2626</v>
       </c>
       <c r="C1002" t="s">
         <v>721</v>
@@ -32942,10 +32942,10 @@
     </row>
     <row r="1003" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
       <c r="B1003" t="s">
-        <v>2630</v>
+        <v>2628</v>
       </c>
       <c r="C1003" t="s">
         <v>721</v>
@@ -32962,16 +32962,16 @@
     </row>
     <row r="1004" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
       <c r="B1004" t="s">
-        <v>2634</v>
+        <v>2632</v>
       </c>
       <c r="C1004" t="s">
         <v>721</v>
       </c>
       <c r="D1004" s="6" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="E1004" s="4" t="s">
         <v>721</v>
@@ -32985,10 +32985,10 @@
     </row>
     <row r="1005" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B1005" t="s">
         <v>2633</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>2635</v>
       </c>
       <c r="C1005" t="s">
         <v>721</v>
@@ -33000,7 +33000,7 @@
         <v>142</v>
       </c>
       <c r="F1005" s="4" t="s">
-        <v>2636</v>
+        <v>2634</v>
       </c>
       <c r="H1005" s="2">
         <v>135</v>
@@ -33011,10 +33011,10 @@
     </row>
     <row r="1006" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
       <c r="B1006" t="s">
-        <v>2638</v>
+        <v>2636</v>
       </c>
       <c r="C1006" t="s">
         <v>721</v>
@@ -33037,16 +33037,16 @@
     </row>
     <row r="1007" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
       <c r="B1007" t="s">
-        <v>2640</v>
+        <v>2638</v>
       </c>
       <c r="C1007" t="s">
         <v>721</v>
       </c>
       <c r="D1007" s="6" t="s">
-        <v>2632</v>
+        <v>2630</v>
       </c>
       <c r="E1007" s="4" t="s">
         <v>721</v>
@@ -33060,16 +33060,16 @@
     </row>
     <row r="1008" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B1008" t="s">
+        <v>2640</v>
+      </c>
+      <c r="C1008" t="s">
+        <v>721</v>
+      </c>
+      <c r="D1008" s="6" t="s">
         <v>2641</v>
-      </c>
-      <c r="B1008" t="s">
-        <v>2642</v>
-      </c>
-      <c r="C1008" t="s">
-        <v>721</v>
-      </c>
-      <c r="D1008" s="6" t="s">
-        <v>2643</v>
       </c>
       <c r="E1008" s="4" t="s">
         <v>721</v>
@@ -33083,10 +33083,10 @@
     </row>
     <row r="1009" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
       <c r="B1009" t="s">
-        <v>2645</v>
+        <v>2643</v>
       </c>
       <c r="C1009" t="s">
         <v>721</v>
@@ -33103,10 +33103,10 @@
     </row>
     <row r="1010" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
       <c r="B1010" t="s">
-        <v>2649</v>
+        <v>2647</v>
       </c>
       <c r="C1010" t="s">
         <v>721</v>
@@ -33123,10 +33123,10 @@
     </row>
     <row r="1011" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
       <c r="B1011" t="s">
-        <v>2650</v>
+        <v>2648</v>
       </c>
       <c r="C1011" t="s">
         <v>721</v>
@@ -33149,10 +33149,10 @@
     </row>
     <row r="1012" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
       <c r="B1012" t="s">
-        <v>2651</v>
+        <v>2649</v>
       </c>
       <c r="C1012" t="s">
         <v>721</v>
@@ -33177,10 +33177,10 @@
     </row>
     <row r="1014" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
       <c r="B1014" t="s">
-        <v>2681</v>
+        <v>2679</v>
       </c>
       <c r="C1014" t="s">
         <v>721</v>
@@ -33195,18 +33195,18 @@
         <v>1634</v>
       </c>
       <c r="H1014" s="2" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="I1014" s="2" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
     </row>
     <row r="1015" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
       <c r="B1015" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="C1015" t="s">
         <v>721</v>
@@ -33221,18 +33221,18 @@
         <v>143</v>
       </c>
       <c r="H1015" s="2" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="I1015" s="2" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="1016" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
       <c r="B1016" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="C1016" t="s">
         <v>721</v>
@@ -33247,18 +33247,18 @@
         <v>143</v>
       </c>
       <c r="H1016" s="2" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
       <c r="I1016" s="2" t="s">
-        <v>2675</v>
+        <v>2673</v>
       </c>
     </row>
     <row r="1017" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
       <c r="B1017" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="C1017" t="s">
         <v>721</v>
@@ -33273,18 +33273,18 @@
         <v>143</v>
       </c>
       <c r="H1017" s="2" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="I1017" s="2" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="1018" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
       <c r="B1018" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="C1018" t="s">
         <v>721</v>
@@ -33299,18 +33299,18 @@
         <v>143</v>
       </c>
       <c r="H1018" s="2" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
       <c r="I1018" s="2" t="s">
-        <v>2676</v>
+        <v>2674</v>
       </c>
     </row>
     <row r="1019" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
       <c r="B1019" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="C1019" t="s">
         <v>721</v>
@@ -33325,18 +33325,18 @@
         <v>143</v>
       </c>
       <c r="H1019" s="2" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="I1019" s="2" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="1020" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="B1020" t="s">
-        <v>2682</v>
+        <v>2680</v>
       </c>
       <c r="C1020" t="s">
         <v>721</v>
@@ -33351,18 +33351,18 @@
         <v>143</v>
       </c>
       <c r="H1020" s="2" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
       <c r="I1020" s="2" t="s">
-        <v>2677</v>
+        <v>2675</v>
       </c>
     </row>
     <row r="1021" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
       <c r="B1021" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="C1021" t="s">
         <v>721</v>
@@ -33374,21 +33374,21 @@
         <v>1190</v>
       </c>
       <c r="F1021" s="4" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="H1021" s="2" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="I1021" s="2" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="1022" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
       <c r="B1022" t="s">
-        <v>2683</v>
+        <v>2681</v>
       </c>
       <c r="C1022" t="s">
         <v>721</v>
@@ -33400,21 +33400,21 @@
         <v>1190</v>
       </c>
       <c r="F1022" s="4" t="s">
-        <v>2606</v>
+        <v>2604</v>
       </c>
       <c r="H1022" s="2" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="I1022" s="2" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="1023" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
       <c r="B1023" t="s">
-        <v>2608</v>
+        <v>2606</v>
       </c>
       <c r="C1023" t="s">
         <v>721</v>
@@ -33426,21 +33426,21 @@
         <v>1190</v>
       </c>
       <c r="F1023" s="4" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="H1023" s="3" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
       <c r="I1023" s="3" t="s">
-        <v>2699</v>
+        <v>2697</v>
       </c>
     </row>
     <row r="1024" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
       <c r="B1024" t="s">
-        <v>2609</v>
+        <v>2607</v>
       </c>
       <c r="C1024" t="s">
         <v>721</v>
@@ -33452,27 +33452,27 @@
         <v>1190</v>
       </c>
       <c r="F1024" s="4" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="H1024" s="3" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
       <c r="I1024" s="3" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
     </row>
     <row r="1025" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
       <c r="B1025" t="s">
-        <v>2684</v>
+        <v>2682</v>
       </c>
       <c r="C1025" t="s">
         <v>721</v>
       </c>
       <c r="D1025" s="6" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="E1025" s="4" t="s">
         <v>142</v>
@@ -33481,24 +33481,24 @@
         <v>143</v>
       </c>
       <c r="H1025" s="2" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="I1025" s="2" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
     </row>
     <row r="1026" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
       <c r="B1026" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="C1026" t="s">
         <v>721</v>
       </c>
       <c r="D1026" s="6" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="E1026" s="4" t="s">
         <v>142</v>
@@ -33507,10 +33507,10 @@
         <v>143</v>
       </c>
       <c r="H1026" s="2" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
       <c r="I1026" s="2" t="s">
-        <v>2680</v>
+        <v>2678</v>
       </c>
     </row>
     <row r="1028" spans="1:9" x14ac:dyDescent="0.25">
@@ -33890,7 +33890,7 @@
         <v>721</v>
       </c>
       <c r="D1045" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="E1045" s="4" t="s">
         <v>721</v>
@@ -34033,7 +34033,7 @@
         <v>721</v>
       </c>
       <c r="D1052" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="E1052" s="4" t="s">
         <v>721</v>
@@ -34061,10 +34061,10 @@
     </row>
     <row r="1054" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1054" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="B1054" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="C1054" t="s">
         <v>721</v>
@@ -34208,7 +34208,7 @@
         <v>721</v>
       </c>
       <c r="D1060" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="E1060" s="4" t="s">
         <v>721</v>
@@ -34242,10 +34242,10 @@
     </row>
     <row r="1062" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1062" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="B1062" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="C1062" t="s">
         <v>721</v>
@@ -34429,7 +34429,7 @@
         <v>721</v>
       </c>
       <c r="D1070" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="E1070" s="4" t="s">
         <v>721</v>
@@ -34443,10 +34443,10 @@
     </row>
     <row r="1071" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1071" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B1071" t="s">
         <v>2383</v>
-      </c>
-      <c r="B1071" t="s">
-        <v>2384</v>
       </c>
       <c r="C1071" t="s">
         <v>721</v>
@@ -34532,7 +34532,7 @@
         <v>721</v>
       </c>
       <c r="D1075" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="E1075" s="4" t="s">
         <v>721</v>
@@ -34704,7 +34704,7 @@
         <v>721</v>
       </c>
       <c r="D1083" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="E1083" s="4" t="s">
         <v>721</v>
@@ -34833,7 +34833,7 @@
         <v>721</v>
       </c>
       <c r="D1089" t="s">
-        <v>2249</v>
+        <v>2248</v>
       </c>
       <c r="E1089" s="4" t="s">
         <v>721</v>
@@ -35135,7 +35135,7 @@
     </row>
     <row r="1103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1103" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
       <c r="B1103" t="s">
         <v>527</v>
@@ -35170,7 +35170,7 @@
         <v>721</v>
       </c>
       <c r="D1104" t="s">
-        <v>2250</v>
+        <v>2249</v>
       </c>
       <c r="E1104" s="4" t="s">
         <v>721</v>
@@ -35261,10 +35261,10 @@
     </row>
     <row r="1109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1109" t="s">
         <v>2097</v>
-      </c>
-      <c r="B1109" t="s">
-        <v>2098</v>
       </c>
       <c r="C1109" t="s">
         <v>721</v>
@@ -35438,10 +35438,10 @@
     </row>
     <row r="1118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1118" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
       <c r="B1118" t="s">
-        <v>2459</v>
+        <v>2457</v>
       </c>
       <c r="C1118" t="s">
         <v>721</v>
@@ -35453,7 +35453,7 @@
         <v>1840</v>
       </c>
       <c r="F1118" s="4" t="s">
-        <v>2460</v>
+        <v>2458</v>
       </c>
       <c r="H1118" s="2">
         <v>60</v>
@@ -35490,10 +35490,10 @@
     </row>
     <row r="1120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1120" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
       <c r="B1120" t="s">
-        <v>2462</v>
+        <v>2460</v>
       </c>
       <c r="C1120" t="s">
         <v>721</v>
@@ -35505,7 +35505,7 @@
         <v>1840</v>
       </c>
       <c r="F1120" s="4" t="s">
-        <v>2463</v>
+        <v>2461</v>
       </c>
       <c r="H1120" s="2">
         <v>30</v>
@@ -35516,10 +35516,10 @@
     </row>
     <row r="1121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1121" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B1121" t="s">
         <v>2243</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>2244</v>
       </c>
       <c r="C1121" t="s">
         <v>721</v>
@@ -35530,10 +35530,10 @@
     </row>
     <row r="1122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1122" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1122" t="s">
         <v>2058</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>2059</v>
       </c>
       <c r="C1122" t="s">
         <v>721</v>
@@ -35631,16 +35631,16 @@
     </row>
     <row r="1126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1126" t="s">
+        <v>2351</v>
+      </c>
+      <c r="B1126" t="s">
         <v>2352</v>
       </c>
-      <c r="B1126" t="s">
+      <c r="C1126" t="s">
+        <v>721</v>
+      </c>
+      <c r="D1126" t="s">
         <v>2353</v>
-      </c>
-      <c r="C1126" t="s">
-        <v>721</v>
-      </c>
-      <c r="D1126" t="s">
-        <v>2354</v>
       </c>
       <c r="E1126" s="4" t="s">
         <v>721</v>
@@ -35654,10 +35654,10 @@
     </row>
     <row r="1127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1127" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B1127" t="s">
         <v>2355</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>2356</v>
       </c>
       <c r="C1127" t="s">
         <v>721</v>
@@ -35717,10 +35717,10 @@
     </row>
     <row r="1130" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1130" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="B1130" s="13" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="C1130" t="s">
         <v>721</v>
@@ -35737,10 +35737,10 @@
     </row>
     <row r="1131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1131" t="s">
+        <v>2349</v>
+      </c>
+      <c r="B1131" t="s">
         <v>2350</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>2351</v>
       </c>
       <c r="C1131" t="s">
         <v>721</v>
@@ -35875,10 +35875,10 @@
     </row>
     <row r="1137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1137" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B1137" t="s">
         <v>2245</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>2246</v>
       </c>
       <c r="C1137" t="s">
         <v>721</v>
@@ -36079,10 +36079,10 @@
     </row>
     <row r="1146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1146" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B1146" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="C1146" t="s">
         <v>721</v>
@@ -36105,10 +36105,10 @@
     </row>
     <row r="1147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1147" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B1147" t="s">
         <v>2233</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>2234</v>
       </c>
       <c r="C1147" t="s">
         <v>721</v>
@@ -36137,7 +36137,7 @@
         <v>721</v>
       </c>
       <c r="D1148" t="s">
-        <v>2251</v>
+        <v>2250</v>
       </c>
       <c r="E1148" s="4" t="s">
         <v>721</v>
@@ -36511,16 +36511,16 @@
     </row>
     <row r="1165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1165" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B1165" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C1165" t="s">
+        <v>721</v>
+      </c>
+      <c r="D1165" t="s">
         <v>2146</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>2176</v>
-      </c>
-      <c r="C1165" t="s">
-        <v>721</v>
-      </c>
-      <c r="D1165" t="s">
-        <v>2147</v>
       </c>
       <c r="E1165" s="4" t="s">
         <v>721</v>
@@ -36551,10 +36551,10 @@
     </row>
     <row r="1167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1167" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B1167" t="s">
         <v>2054</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>2055</v>
       </c>
       <c r="C1167" t="s">
         <v>721</v>
@@ -36568,10 +36568,10 @@
     </row>
     <row r="1168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1168" t="s">
+        <v>2055</v>
+      </c>
+      <c r="B1168" t="s">
         <v>2056</v>
-      </c>
-      <c r="B1168" t="s">
-        <v>2057</v>
       </c>
       <c r="C1168" t="s">
         <v>721</v>
@@ -36653,10 +36653,10 @@
     </row>
     <row r="1173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1173" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
       <c r="B1173" t="s">
-        <v>2664</v>
+        <v>2662</v>
       </c>
       <c r="C1173" t="s">
         <v>721</v>
@@ -36806,10 +36806,10 @@
     </row>
     <row r="1182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1182" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B1182" t="s">
         <v>2064</v>
-      </c>
-      <c r="B1182" t="s">
-        <v>2065</v>
       </c>
       <c r="C1182" t="s">
         <v>721</v>
@@ -36908,10 +36908,10 @@
     </row>
     <row r="1188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1188" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B1188" t="s">
         <v>2066</v>
-      </c>
-      <c r="B1188" t="s">
-        <v>2067</v>
       </c>
       <c r="C1188" t="s">
         <v>721</v>
@@ -36959,10 +36959,10 @@
     </row>
     <row r="1191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1191" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
       <c r="B1191" t="s">
-        <v>2666</v>
+        <v>2664</v>
       </c>
       <c r="C1191" t="s">
         <v>721</v>
@@ -36976,10 +36976,10 @@
     </row>
     <row r="1192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1192" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B1192" t="s">
         <v>2091</v>
-      </c>
-      <c r="B1192" t="s">
-        <v>2092</v>
       </c>
       <c r="C1192" t="s">
         <v>721</v>
@@ -36993,10 +36993,10 @@
     </row>
     <row r="1193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1193" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B1193" t="s">
         <v>2376</v>
-      </c>
-      <c r="B1193" t="s">
-        <v>2377</v>
       </c>
       <c r="C1193" t="s">
         <v>721</v>
@@ -37078,10 +37078,10 @@
     </row>
     <row r="1199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1199" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B1199" t="s">
         <v>2369</v>
-      </c>
-      <c r="B1199" t="s">
-        <v>2370</v>
       </c>
       <c r="C1199" t="s">
         <v>721</v>
@@ -37337,16 +37337,16 @@
     </row>
     <row r="1214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1214" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>721</v>
+      </c>
+      <c r="D1214" t="s">
         <v>2155</v>
-      </c>
-      <c r="B1214" t="s">
-        <v>2157</v>
-      </c>
-      <c r="C1214" t="s">
-        <v>721</v>
-      </c>
-      <c r="D1214" t="s">
-        <v>2156</v>
       </c>
       <c r="E1214" s="4" t="s">
         <v>721</v>
@@ -37631,7 +37631,7 @@
         <v>1211</v>
       </c>
       <c r="B1226" t="s">
-        <v>2072</v>
+        <v>2071</v>
       </c>
       <c r="C1226" t="s">
         <v>721</v>
@@ -37674,7 +37674,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
@@ -37684,722 +37684,722 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2752</v>
+        <v>2750</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>2445</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2441</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2667</v>
+        <v>2665</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>2669</v>
+        <v>2667</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>2703</v>
+        <v>2701</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>2712</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2714</v>
+        <v>2712</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>2470</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>2475</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2480</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>2385</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2759</v>
+        <v>2757</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2512</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>2518</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2486</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>2455</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>2454</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2399</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>2401</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2405</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>2490</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>2408</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>2411</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>2414</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>2417</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>2396</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>2390</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>2393</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>2420</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>2434</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>2436</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>2439</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>2443</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>2483</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>2464</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>2387</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>2731</v>
+        <v>2729</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>2525</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>2686</v>
+        <v>2684</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>2687</v>
+        <v>2685</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>2694</v>
+        <v>2692</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>2689</v>
+        <v>2687</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>2690</v>
+        <v>2688</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>2693</v>
+        <v>2691</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>2697</v>
+        <v>2695</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>2695</v>
+        <v>2693</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>2696</v>
+        <v>2694</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>2688</v>
+        <v>2686</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>2691</v>
+        <v>2689</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>2621</v>
+        <v>2619</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>2624</v>
+        <v>2622</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>2652</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>2653</v>
+        <v>2651</v>
       </c>
     </row>
     <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>2639</v>
+        <v>2637</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>2641</v>
+        <v>2639</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2646</v>
+        <v>2644</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>2647</v>
+        <v>2645</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>2648</v>
+        <v>2646</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>2631</v>
+        <v>2629</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>2633</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>2637</v>
+        <v>2635</v>
       </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>2644</v>
+        <v>2642</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>2629</v>
+        <v>2627</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>2627</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>2619</v>
+        <v>2617</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>2600</v>
+        <v>2598</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>2602</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>2658</v>
+        <v>2656</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>2604</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>2383</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>2461</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>2458</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>2663</v>
+        <v>2661</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>2665</v>
+        <v>2663</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
@@ -38895,12 +38895,12 @@
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
@@ -38940,7 +38940,7 @@
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -38955,22 +38955,22 @@
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>2169</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>2380</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>2069</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -38980,17 +38980,17 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>2060</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
@@ -39020,7 +39020,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
@@ -39030,7 +39030,7 @@
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.25">
@@ -39050,107 +39050,107 @@
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>2127</v>
+        <v>2126</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>2363</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>2365</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>2348</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>2227</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.25">
@@ -39165,57 +39165,57 @@
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
     </row>
     <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>2121</v>
+        <v>2120</v>
       </c>
     </row>
     <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="73" spans="1:1" x14ac:dyDescent="0.25">
@@ -39230,57 +39230,57 @@
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>2110</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>2106</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>2252</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="86" spans="1:1" x14ac:dyDescent="0.25">
@@ -39295,137 +39295,137 @@
     </row>
     <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>2023</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
     </row>
     <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>2031</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>2019</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>2039</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>2034</v>
+        <v>2033</v>
       </c>
     </row>
     <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>2040</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
     </row>
     <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>2037</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>2012</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>2038</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>2033</v>
+        <v>2032</v>
       </c>
     </row>
     <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>2029</v>
+        <v>2028</v>
       </c>
     </row>
     <row r="115" spans="1:1" x14ac:dyDescent="0.25">
@@ -39440,7 +39440,7 @@
     </row>
     <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
     </row>
     <row r="118" spans="1:1" x14ac:dyDescent="0.25">
@@ -39450,32 +39450,32 @@
     </row>
     <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>2028</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>2022</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
@@ -39490,27 +39490,27 @@
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>2025</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>2011</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>2018</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>2032</v>
+        <v>2031</v>
       </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
@@ -39520,32 +39520,32 @@
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>2026</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>2371</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>2372</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>2373</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
@@ -39585,12 +39585,12 @@
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>2093</v>
+        <v>2092</v>
       </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
@@ -39600,7 +39600,7 @@
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>2050</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
@@ -39615,32 +39615,32 @@
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>2205</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>2203</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
@@ -39690,12 +39690,12 @@
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>2210</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
@@ -39825,7 +39825,7 @@
     </row>
     <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="195" spans="1:1" x14ac:dyDescent="0.25">
@@ -39925,12 +39925,12 @@
     </row>
     <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>2378</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="216" spans="1:1" x14ac:dyDescent="0.25">
@@ -39975,7 +39975,7 @@
     </row>
     <row r="224" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="225" spans="1:1" x14ac:dyDescent="0.25">
@@ -40000,32 +40000,32 @@
     </row>
     <row r="229" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
     </row>
     <row r="230" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>2241</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="231" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="232" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="233" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="234" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="235" spans="1:1" x14ac:dyDescent="0.25">
@@ -40035,7 +40035,7 @@
     </row>
     <row r="236" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="237" spans="1:1" x14ac:dyDescent="0.25">
@@ -40045,17 +40045,17 @@
     </row>
     <row r="238" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="239" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>2358</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="240" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>2359</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="241" spans="1:1" x14ac:dyDescent="0.25">
@@ -40065,7 +40065,7 @@
     </row>
     <row r="242" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="243" spans="1:1" x14ac:dyDescent="0.25">
@@ -40080,7 +40080,7 @@
     </row>
     <row r="245" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>2077</v>
+        <v>2076</v>
       </c>
     </row>
     <row r="246" spans="1:1" x14ac:dyDescent="0.25">
@@ -40100,7 +40100,7 @@
     </row>
     <row r="249" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="250" spans="1:1" x14ac:dyDescent="0.25">
@@ -40155,32 +40155,32 @@
     </row>
     <row r="260" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="261" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
     </row>
     <row r="262" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="263" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>2058</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="264" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>2352</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="265" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>2355</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="266" spans="1:1" x14ac:dyDescent="0.25">
@@ -40195,32 +40195,32 @@
     </row>
     <row r="268" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>2350</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="269" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>2369</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="270" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>2064</v>
+        <v>2063</v>
       </c>
     </row>
     <row r="271" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="272" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="273" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="274" spans="1:1" x14ac:dyDescent="0.25">
@@ -40240,7 +40240,7 @@
     </row>
     <row r="277" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
     </row>
     <row r="278" spans="1:1" x14ac:dyDescent="0.25">
@@ -40255,17 +40255,17 @@
     </row>
     <row r="280" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="281" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="282" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
     </row>
     <row r="285" spans="1:1" x14ac:dyDescent="0.25">
@@ -40580,12 +40580,12 @@
     </row>
     <row r="349" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="350" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
     </row>
     <row r="351" spans="1:1" x14ac:dyDescent="0.25">
@@ -40725,12 +40725,12 @@
     </row>
     <row r="378" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
     </row>
     <row r="379" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="380" spans="1:1" x14ac:dyDescent="0.25">
@@ -40845,12 +40845,12 @@
     </row>
     <row r="402" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="403" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="404" spans="1:1" x14ac:dyDescent="0.25">
@@ -40990,12 +40990,12 @@
     </row>
     <row r="431" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="432" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="433" spans="1:1" x14ac:dyDescent="0.25">
